--- a/CNA/RBS-TargetsAnalysis-CNA.xlsx
+++ b/CNA/RBS-TargetsAnalysis-CNA.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive - Universidade de Lisboa\NUCRIA\TESE\Activations\116Sn(p,g)117Sb_Analysis\CNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2C0BF43847FE627874208A2A5B53FC3E62A9D58A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="7310" tabRatio="668"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="6700" tabRatio="668" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sn+Al targets" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +30,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="46">
   <si>
+    <t xml:space="preserve">Tin density = </t>
+  </si>
+  <si>
     <t>g/cm^3</t>
+  </si>
+  <si>
+    <t>Al   density =</t>
+  </si>
+  <si>
+    <t>Surface approximation</t>
+  </si>
+  <si>
+    <t>Chu et al, Backscattering spectometry, 1978</t>
+  </si>
+  <si>
+    <t>Ebeam =</t>
+  </si>
+  <si>
+    <t>MeV</t>
   </si>
   <si>
     <t>Element</t>
@@ -47,10 +69,22 @@
     <t>Surface channel</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>O</t>
   </si>
   <si>
-    <t>Delta_E (keV)</t>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Sn</t>
+  </si>
+  <si>
+    <t>Pt</t>
   </si>
   <si>
     <t>(dE/dx)_in [E_0] (MeV cm^2 / g)</t>
@@ -66,36 +100,6 @@
   </si>
   <si>
     <t>[S] (eV/nm)</t>
-  </si>
-  <si>
-    <t>x (nm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tin density = </t>
-  </si>
-  <si>
-    <t>Sn</t>
-  </si>
-  <si>
-    <t>Sn channel in</t>
-  </si>
-  <si>
-    <t>Sn channel out</t>
-  </si>
-  <si>
-    <t>Al</t>
-  </si>
-  <si>
-    <t>Al channel in</t>
-  </si>
-  <si>
-    <t>Al channel out</t>
-  </si>
-  <si>
-    <t>Al   density =</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <r>
@@ -148,22 +152,52 @@
     </r>
   </si>
   <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>Pt</t>
-  </si>
-  <si>
-    <t>Ebeam =</t>
-  </si>
-  <si>
-    <t>MeV</t>
-  </si>
-  <si>
     <t>116Sn-C3</t>
   </si>
   <si>
+    <t>Sn channel in</t>
+  </si>
+  <si>
+    <t>Sn channel out</t>
+  </si>
+  <si>
+    <t>Delta_E (keV)</t>
+  </si>
+  <si>
+    <t>Analytical</t>
+  </si>
+  <si>
+    <t>SimNRA</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Al channel in</t>
+  </si>
+  <si>
+    <t>Al channel out</t>
+  </si>
+  <si>
+    <t>+-</t>
+  </si>
+  <si>
+    <t>nm</t>
+  </si>
+  <si>
+    <t>mg/cm2</t>
+  </si>
+  <si>
+    <t>ug/cm2</t>
+  </si>
+  <si>
     <t>116Sn-C10</t>
+  </si>
+  <si>
+    <t>x (nm)</t>
+  </si>
+  <si>
+    <t>SimNRA (nm)</t>
   </si>
   <si>
     <t>116Sn-D4</t>
@@ -177,47 +211,17 @@
   <si>
     <t>116Sn-D5</t>
   </si>
-  <si>
-    <t>mg/cm2</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>ug/cm2</t>
-  </si>
-  <si>
-    <t>SimNRA (nm)</t>
-  </si>
-  <si>
-    <t>+-</t>
-  </si>
-  <si>
-    <t>Analytical</t>
-  </si>
-  <si>
-    <t>SimNRA</t>
-  </si>
-  <si>
-    <t>nm</t>
-  </si>
-  <si>
-    <t>Chu et al, Backscattering spectometry, 1978</t>
-  </si>
-  <si>
-    <t>Surface approximation</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -849,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -911,7 +915,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -924,20 +928,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -955,25 +958,25 @@
     <xf numFmtId="1" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1052,16 +1055,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1072,22 +1072,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1119,7 +1114,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1134,7 +1129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1206,6 +1201,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="20" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1304,7 +1302,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -1317,37 +1315,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -1357,9 +1324,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>RBS Calib Ebeam = 3.2 MeV</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -1398,8 +1362,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.15704155730533684"/>
-                  <c:y val="-0.19377333041703121"/>
+                  <c:x val="4.4871574459306125E-2"/>
+                  <c:y val="0.22178476420352305"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1472,7 +1436,7 @@
                   <c:v>2501.9455642234693</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2673.6770834573981</c:v>
+                  <c:v>2684.5156889253863</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2781.8531330246997</c:v>
@@ -1487,6 +1451,18 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:v>RBS Calib Ebeam = 3.2 MeV</c:v>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4725-42AB-9D79-6C221B20457F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1496,11 +1472,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-519145264"/>
-        <c:axId val="-307680048"/>
+        <c:axId val="1680979504"/>
+        <c:axId val="1931910496"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-519145264"/>
+        <c:axId val="1680979504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="300"/>
@@ -1547,7 +1523,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1614,12 +1589,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-307680048"/>
+        <c:crossAx val="1931910496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-307680048"/>
+        <c:axId val="1931910496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2000"/>
@@ -1666,7 +1641,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1733,7 +1707,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-519145264"/>
+        <c:crossAx val="1680979504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1783,7 +1757,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -1822,7 +1796,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1940,7 +1913,7 @@
                   <c:v>2736.5029608694194</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3025.1570117547149</c:v>
+                  <c:v>2949.3725069573857</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3042.6518642457654</c:v>
@@ -1955,6 +1928,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BE12-4DDB-8804-EB87D64C3DA7}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1964,11 +1942,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-307677328"/>
-        <c:axId val="-266083728"/>
+        <c:axId val="1931907776"/>
+        <c:axId val="1931912672"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-307677328"/>
+        <c:axId val="1931907776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="300"/>
@@ -2015,7 +1993,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2082,12 +2059,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266083728"/>
+        <c:crossAx val="1931912672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-266083728"/>
+        <c:axId val="1931912672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2000"/>
@@ -2134,7 +2111,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2201,7 +2177,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-307677328"/>
+        <c:crossAx val="1931907776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2251,7 +2227,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -2290,7 +2266,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2408,7 +2383,7 @@
                   <c:v>3049.2461563973534</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3370.8892416695394</c:v>
+                  <c:v>3303.5319599763839</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3390.3835058738528</c:v>
@@ -2423,6 +2398,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-76F0-4A6A-A212-00E256F66E45}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2432,11 +2412,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-266095152"/>
-        <c:axId val="-266094064"/>
+        <c:axId val="1931909952"/>
+        <c:axId val="1931905600"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-266095152"/>
+        <c:axId val="1931909952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="280"/>
@@ -2483,7 +2463,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2550,12 +2529,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266094064"/>
+        <c:crossAx val="1931905600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-266094064"/>
+        <c:axId val="1931905600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2500"/>
@@ -2602,7 +2581,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2669,7 +2647,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266095152"/>
+        <c:crossAx val="1931909952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2719,7 +2697,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -2758,7 +2736,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2876,7 +2853,7 @@
                   <c:v>3361.9893519252869</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3716.6214715843644</c:v>
+                  <c:v>3656.1269746550179</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3738.1151475019406</c:v>
@@ -2891,6 +2868,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8E2B-4648-A977-1C81E9E14071}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2900,11 +2882,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-266095696"/>
-        <c:axId val="-266094608"/>
+        <c:axId val="1931902336"/>
+        <c:axId val="1931906144"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-266095696"/>
+        <c:axId val="1931902336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="300"/>
@@ -2951,7 +2933,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3018,12 +2999,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266094608"/>
+        <c:crossAx val="1931906144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-266094608"/>
+        <c:axId val="1931906144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="3000"/>
@@ -3070,7 +3051,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3137,7 +3117,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266095696"/>
+        <c:crossAx val="1931902336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3187,7 +3167,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -3226,7 +3206,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3388,7 +3367,7 @@
                   <c:v>3674.7325474532204</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4062.3537014991889</c:v>
+                  <c:v>3989.32641123543</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4543.3579823269692</c:v>
@@ -3400,6 +3379,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B84B-44E0-8449-B0458021BBDE}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3409,11 +3393,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-266081552"/>
-        <c:axId val="-266085360"/>
+        <c:axId val="1931911040"/>
+        <c:axId val="1931911584"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-266081552"/>
+        <c:axId val="1931911040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="300"/>
@@ -3460,7 +3444,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3527,12 +3510,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266085360"/>
+        <c:crossAx val="1931911584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-266085360"/>
+        <c:axId val="1931911584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="3000"/>
@@ -3579,7 +3562,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3646,7 +3628,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266081552"/>
+        <c:crossAx val="1931911040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3696,7 +3678,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
@@ -3735,7 +3717,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3889,7 +3870,7 @@
                   <c:v>3909.289944099171</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4321.6528739353071</c:v>
+                  <c:v>4245.159618066652</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4346.6455203510932</c:v>
@@ -3904,6 +3885,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B09C-41B2-B6D7-455854937C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -3913,11 +3899,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-266093520"/>
-        <c:axId val="-266089168"/>
+        <c:axId val="1931913216"/>
+        <c:axId val="1931900704"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-266093520"/>
+        <c:axId val="1931913216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="300"/>
@@ -3964,7 +3950,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4031,12 +4016,12 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266089168"/>
+        <c:crossAx val="1931900704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-266089168"/>
+        <c:axId val="1931900704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="3500"/>
@@ -4083,7 +4068,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4150,7 +4134,7 @@
             <a:endParaRPr lang="pt-PT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-266093520"/>
+        <c:crossAx val="1931913216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7552,7 +7536,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2"/>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -7582,7 +7572,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3"/>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7614,7 +7610,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Gráfico 4"/>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7646,7 +7648,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 5"/>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7678,7 +7686,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Gráfico 6"/>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7710,7 +7724,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Gráfico 7"/>
+        <xdr:cNvPr id="8" name="Gráfico 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -7742,7 +7762,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1"/>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8035,282 +8061,205 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH115"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.08984375" customWidth="1"/>
-    <col min="18" max="18" width="2.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.26953125" style="83" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.26953125" style="80" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.453125" customWidth="1"/>
-    <col min="28" max="28" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.81640625" customWidth="1"/>
-    <col min="38" max="39" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.1796875" customWidth="1"/>
-    <col min="42" max="42" width="6.453125" customWidth="1"/>
-    <col min="43" max="44" width="8.453125" customWidth="1"/>
-    <col min="45" max="45" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="80" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="78" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.42578125" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.85546875" customWidth="1"/>
+    <col min="38" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.140625" customWidth="1"/>
+    <col min="42" max="42" width="6.42578125" customWidth="1"/>
+    <col min="43" max="44" width="8.42578125" customWidth="1"/>
+    <col min="45" max="45" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="126">
+    <row r="1" spans="1:34" ht="29.45" thickBot="1">
+      <c r="A1" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="121">
         <v>7.31</v>
       </c>
-      <c r="C1" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>22</v>
+      <c r="C1" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>2</v>
       </c>
       <c r="E1" s="12">
         <v>2.6989999999999998</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M2" s="62"/>
-      <c r="N2" s="133" t="s">
-        <v>44</v>
-      </c>
-      <c r="O2" s="134"/>
-      <c r="P2" s="135"/>
-    </row>
-    <row r="3" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="60"/>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="60"/>
-      <c r="AD3" s="60"/>
-      <c r="AE3" s="60"/>
-      <c r="AF3" s="60"/>
-      <c r="AG3" s="60"/>
-      <c r="AH3" s="128"/>
-    </row>
-    <row r="4" spans="1:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="15" thickBot="1">
+      <c r="M2" s="61"/>
+      <c r="N2" s="128" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="129"/>
+      <c r="P2" s="130"/>
+    </row>
+    <row r="3" spans="1:34" ht="15" thickBot="1">
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="59"/>
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="59"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="123"/>
+    </row>
+    <row r="4" spans="1:34" ht="29.45" thickBot="1">
       <c r="B4" s="25"/>
-      <c r="C4" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="57">
+      <c r="C4" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="56">
         <v>3.2</v>
       </c>
-      <c r="E4" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="26"/>
+      <c r="E4" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G4" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH4" s="124"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="B5" s="25"/>
+      <c r="G5" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="45">
         <v>6</v>
       </c>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="82"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="129"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="46">
-        <v>6</v>
-      </c>
-      <c r="I5" s="46">
+      <c r="I5" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="46">
         <f>((SQRT(1-(1/I5)^2*SIN(RADIANS(165))^2)+1/I5*COS(RADIANS(165)))/(1+1/I5))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="49">
         <f t="shared" ref="K5:K10" si="0">$D$4*1000*J5</f>
         <v>2304.8706081305609</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="47">
         <v>317.5</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="129"/>
-    </row>
-    <row r="6" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH5" s="124"/>
+    </row>
+    <row r="6" spans="1:34" ht="15" thickBot="1">
       <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="41">
+      <c r="G6" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="40">
         <v>8</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="42">
         <f t="shared" ref="J6:J8" si="1">((SQRT(1-(1/I6)^2*SIN(RADIANS(165))^2)+1/I6*COS(RADIANS(165)))/(1+1/I6))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K6" s="51">
+      <c r="K6" s="50">
         <f t="shared" si="0"/>
         <v>2501.9455642234693</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="43">
         <v>346.5</v>
       </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="82"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="129"/>
-    </row>
-    <row r="7" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH6" s="124"/>
+    </row>
+    <row r="7" spans="1:34" ht="15" thickBot="1">
       <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="131">
+      <c r="D7" s="126">
         <f t="array" ref="D7:E10">LINEST(K5:K10,L5:L10,TRUE,TRUE)</f>
-        <v>6.7295795531372953</v>
-      </c>
-      <c r="E7" s="132">
-        <v>166.16581417456018</v>
-      </c>
-      <c r="F7" s="26"/>
+        <v>6.7224382069060375</v>
+      </c>
+      <c r="E7" s="127">
+        <v>170.71274003546978</v>
+      </c>
       <c r="G7" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H7" s="21">
         <v>13</v>
@@ -8318,266 +8267,145 @@
       <c r="I7" s="21">
         <v>26.98</v>
       </c>
-      <c r="J7" s="39">
+      <c r="J7" s="38">
         <f t="shared" si="1"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K7" s="52">
-        <f>$K$9*J7</f>
-        <v>2673.6770834573981</v>
+      <c r="K7" s="51">
+        <f>(3200-94.11)*J7</f>
+        <v>2684.5156889253863</v>
       </c>
       <c r="L7" s="23">
         <v>376</v>
       </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="129"/>
-    </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AH7" s="124"/>
+    </row>
+    <row r="8" spans="1:34" ht="15.75" customHeight="1">
       <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
       <c r="D8" s="25">
-        <v>0.13198714197934402</v>
-      </c>
-      <c r="E8" s="129">
-        <v>50.986080861768841</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="28">
+        <v>9.4757415506544138E-2</v>
+      </c>
+      <c r="E8" s="124">
+        <v>36.60439325237445</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="27">
         <v>14</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>28.09</v>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="36">
         <f t="shared" si="1"/>
         <v>0.86932910407021868</v>
       </c>
-      <c r="K8" s="53">
+      <c r="K8" s="52">
         <f t="shared" si="0"/>
         <v>2781.8531330246997</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="28">
         <v>386.5</v>
       </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="82"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="26"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="129"/>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="AH8" s="124"/>
+    </row>
+    <row r="9" spans="1:34">
       <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
       <c r="D9" s="25">
-        <v>0.9984636871861734</v>
-      </c>
-      <c r="E9" s="129">
-        <v>14.31459731733414</v>
-      </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="30">
+        <v>0.99920587705005592</v>
+      </c>
+      <c r="E9" s="124">
+        <v>10.27686656037883</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="29">
         <v>50</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>116</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="30">
         <f>((SQRT(1-(1/I9)^2*SIN(RADIANS(165))^2)+1/I9*COS(RADIANS(165)))/(1+1/I9))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="53">
         <f t="shared" si="0"/>
         <v>3093.350115626873</v>
       </c>
-      <c r="L9" s="35">
+      <c r="L9" s="34">
         <v>434</v>
       </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="85"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="82"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="129"/>
-    </row>
-    <row r="10" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH9" s="124"/>
+    </row>
+    <row r="10" spans="1:34" ht="15" thickBot="1">
       <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="61">
-        <v>2599.6364235204678</v>
-      </c>
-      <c r="E10" s="130">
+      <c r="D10" s="60">
+        <v>5033.0034014027715</v>
+      </c>
+      <c r="E10" s="125">
         <v>4</v>
       </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="33">
         <v>78</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="33">
         <v>195.1</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="37">
         <f>((SQRT(1-(1/I10)^2*SIN(RADIANS(165))^2)+1/I10*COS(RADIANS(165)))/(1+1/I10))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K10" s="55">
+      <c r="K10" s="54">
         <f t="shared" si="0"/>
         <v>3136.1553016829826</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="35">
         <v>442</v>
       </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="85"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="26"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="129"/>
-    </row>
-    <row r="11" spans="1:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH10" s="124"/>
+    </row>
+    <row r="11" spans="1:34" ht="44.1" thickBot="1">
       <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
       <c r="M11" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="26"/>
-      <c r="S11" s="85"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="82"/>
-      <c r="X11" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD11" s="26"/>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="129"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH11" s="124"/>
+    </row>
+    <row r="12" spans="1:34">
       <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
       <c r="M12" s="4">
         <v>46.15</v>
       </c>
@@ -8596,625 +8424,386 @@
         <f>(($J$9/COS(RADIANS(0))*$N$12)+(1/COS(RADIANS(180-165))*$P$12))</f>
         <v>68.255967677964605</v>
       </c>
-      <c r="R12" s="26"/>
-      <c r="S12" s="85"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="82"/>
-      <c r="X12" s="26"/>
       <c r="Y12" s="17">
-        <v>80.72</v>
+        <v>80.48</v>
       </c>
       <c r="Z12" s="11">
         <f>Y12*$E$1/10</f>
-        <v>21.786327999999997</v>
+        <v>21.721551999999999</v>
       </c>
       <c r="AA12" s="17">
-        <v>89.5</v>
+        <v>89.24</v>
       </c>
       <c r="AB12" s="4">
         <f>AA12*$E$1/10</f>
-        <v>24.15605</v>
+        <v>24.085875999999995</v>
       </c>
       <c r="AC12" s="10">
         <f>(($J$7/COS(RADIANS(0))*Z12)+(1/COS(RADIANS(180-165))*AB12))</f>
-        <v>43.838772580534439</v>
-      </c>
-      <c r="AD12" s="26"/>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="129"/>
-    </row>
-    <row r="13" spans="1:34" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>43.710135232537922</v>
+      </c>
+      <c r="AH12" s="124"/>
+    </row>
+    <row r="13" spans="1:34" ht="17.25" customHeight="1">
       <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="85"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="82"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-      <c r="AC13" s="26"/>
-      <c r="AD13" s="26"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="129"/>
-    </row>
-    <row r="14" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH13" s="124"/>
+    </row>
+    <row r="14" spans="1:34" ht="15" thickBot="1">
       <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="85"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
-      <c r="W14" s="82"/>
-      <c r="X14" s="26"/>
-      <c r="Y14" s="26"/>
-      <c r="Z14" s="26"/>
-      <c r="AA14" s="26"/>
-      <c r="AB14" s="26"/>
-      <c r="AC14" s="26"/>
-      <c r="AD14" s="26"/>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="129"/>
-    </row>
-    <row r="15" spans="1:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH14" s="124"/>
+    </row>
+    <row r="15" spans="1:34" ht="29.45" thickBot="1">
       <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
       <c r="M15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="N15" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O15" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P15" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="104" t="s">
-        <v>41</v>
-      </c>
-      <c r="R15" s="70"/>
-      <c r="S15" s="86"/>
-      <c r="T15" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U15" s="97" t="s">
+      <c r="R15" s="69"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="U15" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="93"/>
+      <c r="W15" s="94"/>
+      <c r="Z15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC15" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH15" s="124"/>
+    </row>
+    <row r="16" spans="1:34" ht="15" thickBot="1">
+      <c r="B16" s="25"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="64">
+        <v>434</v>
+      </c>
+      <c r="O16" s="65">
+        <v>420</v>
+      </c>
+      <c r="P16" s="98">
+        <f>(N16-O16)*D7</f>
+        <v>94.114134896684533</v>
+      </c>
+      <c r="Q16" s="104">
+        <f>P16*10^3/Q12</f>
+        <v>1378.8411196618028</v>
+      </c>
+      <c r="R16" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" s="106">
+        <f>Q16/D7*D8</f>
+        <v>19.435719135220641</v>
+      </c>
+      <c r="T16" s="107">
+        <v>1383</v>
+      </c>
+      <c r="U16" s="108">
+        <v>1339</v>
+      </c>
+      <c r="V16" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" s="110">
         <v>37</v>
       </c>
-      <c r="V15" s="98"/>
-      <c r="W15" s="99"/>
-      <c r="X15" s="26"/>
-      <c r="Y15" s="26"/>
-      <c r="Z15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC15" s="72" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD15" s="73"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="101" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="129"/>
-    </row>
-    <row r="16" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="65">
-        <v>434</v>
-      </c>
-      <c r="O16" s="66">
-        <v>420</v>
-      </c>
-      <c r="P16" s="103">
-        <f>(N16-O16)*D7</f>
-        <v>94.214113743922127</v>
-      </c>
-      <c r="Q16" s="109">
-        <f>P16*10^3/Q12</f>
-        <v>1380.3058831196925</v>
-      </c>
-      <c r="R16" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S16" s="111">
-        <f>Q16/D7*D8</f>
-        <v>27.071918406152147</v>
-      </c>
-      <c r="T16" s="112">
-        <v>1383</v>
-      </c>
-      <c r="U16" s="113">
-        <v>1339</v>
-      </c>
-      <c r="V16" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W16" s="115">
-        <v>37</v>
-      </c>
-      <c r="X16" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="116">
+      <c r="X16" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" s="111">
         <v>376</v>
       </c>
       <c r="AA16" s="16">
         <v>368</v>
       </c>
-      <c r="AB16" s="71">
+      <c r="AB16" s="70">
         <f>(Z16-AA16)*D7</f>
-        <v>53.836636425098362</v>
-      </c>
-      <c r="AC16" s="117">
+        <v>53.7795056552483</v>
+      </c>
+      <c r="AC16" s="112">
         <f>AB16*10^3/AC12</f>
-        <v>1228.0598487605293</v>
-      </c>
-      <c r="AD16" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE16" s="122">
+        <v>1230.3669473713894</v>
+      </c>
+      <c r="AD16" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE16" s="117">
         <f>AC16/D7*D8</f>
-        <v>24.08591923724612</v>
-      </c>
-      <c r="AF16" s="123">
+        <v>17.342872997749321</v>
+      </c>
+      <c r="AF16" s="118">
         <v>3.32</v>
       </c>
-      <c r="AG16" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH16" s="129"/>
-    </row>
-    <row r="17" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG16" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH16" s="124"/>
+    </row>
+    <row r="17" spans="2:34" ht="15" thickBot="1">
       <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="74"/>
-      <c r="S17" s="108"/>
-      <c r="T17" s="100"/>
-      <c r="U17" s="100"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="105"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="69"/>
-      <c r="AD17" s="68"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="78"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="129"/>
-    </row>
-    <row r="18" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q17" s="102"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="100"/>
+      <c r="AC17" s="68"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="83"/>
+      <c r="AF17" s="76"/>
+      <c r="AH17" s="124"/>
+    </row>
+    <row r="18" spans="2:34" ht="15" thickBot="1">
       <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="94">
+      <c r="Q18" s="89">
         <f>Q16*$B$1*10^(-7)*10^3</f>
-        <v>1.009003600560495</v>
-      </c>
-      <c r="R18" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S18" s="93">
+        <v>1.0079328584727778</v>
+      </c>
+      <c r="R18" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S18" s="88">
         <f>S16*$B$1*10^(-7)*10^3</f>
-        <v>1.9789572354897218E-2</v>
-      </c>
-      <c r="T18" s="79">
+        <v>1.4207510687846286E-2</v>
+      </c>
+      <c r="T18" s="77">
         <f>T16*$B$1*10^(-7)*10^3</f>
         <v>1.0109729999999999</v>
       </c>
-      <c r="U18" s="95">
+      <c r="U18" s="90">
         <f>U16*$B$1*10^(-7)*10^3</f>
         <v>0.97880899999999993</v>
       </c>
-      <c r="V18" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W18" s="106">
+      <c r="V18" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W18" s="101">
         <f>W16*$B$1*10^(-7)*10^3</f>
         <v>2.7046999999999998E-2</v>
       </c>
-      <c r="X18" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
-      <c r="AB18" s="26"/>
-      <c r="AC18" s="118">
+      <c r="X18" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC18" s="113">
         <f>AC16*$E$1/10</f>
-        <v>331.45335318046688</v>
-      </c>
-      <c r="AD18" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE18" s="120">
+        <v>332.07603909553802</v>
+      </c>
+      <c r="AD18" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE18" s="115">
         <f>AE16*$E$1*10^(-7)*10^6</f>
-        <v>6.5007896021327269</v>
-      </c>
-      <c r="AF18" s="124">
-        <f>AF16*$E$1/10</f>
+        <v>4.6808414220925414</v>
+      </c>
+      <c r="AF18" s="119">
+        <f>AF16*10^(-7)*$E$1*10^6</f>
         <v>0.89606799999999986</v>
       </c>
-      <c r="AG18" s="67" t="s">
+      <c r="AG18" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH18" s="129"/>
-    </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH18" s="124"/>
+    </row>
+    <row r="19" spans="2:34">
       <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="85"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="74"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="89"/>
-      <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="26"/>
-      <c r="AB19" s="26"/>
-      <c r="AC19" s="26"/>
-      <c r="AD19" s="26"/>
-      <c r="AE19" s="26"/>
-      <c r="AF19" s="26"/>
-      <c r="AG19" s="26"/>
-      <c r="AH19" s="129"/>
-    </row>
-    <row r="20" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="75"/>
-      <c r="V20" s="75"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="130"/>
-    </row>
-    <row r="21" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U21" s="77"/>
-      <c r="V21" s="77"/>
-      <c r="W21" s="91"/>
-      <c r="AD21" s="26"/>
-      <c r="AF21" s="26"/>
-    </row>
-    <row r="22" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="59"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="60"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="60"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="60"/>
-      <c r="AE22" s="60"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="128"/>
-    </row>
-    <row r="23" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U19" s="73"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="85"/>
+      <c r="AH19" s="124"/>
+    </row>
+    <row r="20" spans="2:34" ht="15" thickBot="1">
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="84"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="74"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="61"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="61"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="61"/>
+      <c r="AD20" s="61"/>
+      <c r="AE20" s="61"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="125"/>
+    </row>
+    <row r="21" spans="2:34" ht="15" thickBot="1">
+      <c r="U21" s="73"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="85"/>
+    </row>
+    <row r="22" spans="2:34" ht="15" thickBot="1">
+      <c r="B22" s="58"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="79"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="59"/>
+      <c r="AC22" s="59"/>
+      <c r="AD22" s="59"/>
+      <c r="AE22" s="59"/>
+      <c r="AF22" s="59"/>
+      <c r="AG22" s="59"/>
+      <c r="AH22" s="123"/>
+    </row>
+    <row r="23" spans="2:34" ht="29.45" thickBot="1">
       <c r="B23" s="25"/>
-      <c r="C23" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="57">
+      <c r="C23" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="56">
         <v>3.5</v>
       </c>
-      <c r="E23" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="26"/>
+      <c r="E23" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G23" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L23" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH23" s="124"/>
+    </row>
+    <row r="24" spans="2:34">
+      <c r="B24" s="25"/>
+      <c r="G24" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="45">
         <v>6</v>
       </c>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="85"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
-      <c r="W23" s="82"/>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-      <c r="AC23" s="26"/>
-      <c r="AD23" s="26"/>
-      <c r="AE23" s="26"/>
-      <c r="AF23" s="26"/>
-      <c r="AG23" s="26"/>
-      <c r="AH23" s="129"/>
-    </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.35">
-      <c r="B24" s="25"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="46">
-        <v>6</v>
-      </c>
-      <c r="I24" s="46">
+      <c r="I24" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J24" s="47">
+      <c r="J24" s="46">
         <f>((SQRT(1-(1/I24)^2*SIN(RADIANS(165))^2)+1/I24*COS(RADIANS(165)))/(1+1/I24))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K24" s="50">
+      <c r="K24" s="49">
         <f>$D$23*1000*J24</f>
         <v>2520.9522276428006</v>
       </c>
-      <c r="L24" s="48">
+      <c r="L24" s="47">
         <v>350</v>
       </c>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="85"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="82"/>
-      <c r="X24" s="26"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="26"/>
-      <c r="AD24" s="26"/>
-      <c r="AE24" s="26"/>
-      <c r="AF24" s="26"/>
-      <c r="AG24" s="26"/>
-      <c r="AH24" s="129"/>
-    </row>
-    <row r="25" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH24" s="124"/>
+    </row>
+    <row r="25" spans="2:34" ht="15" thickBot="1">
       <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="41">
+      <c r="G25" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="40">
         <v>8</v>
       </c>
-      <c r="I25" s="42">
+      <c r="I25" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="42">
         <f t="shared" ref="J25:J27" si="2">((SQRT(1-(1/I25)^2*SIN(RADIANS(165))^2)+1/I25*COS(RADIANS(165)))/(1+1/I25))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="50">
         <f t="shared" ref="K25:K29" si="3">$D$23*1000*J25</f>
         <v>2736.5029608694194</v>
       </c>
-      <c r="L25" s="44">
+      <c r="L25" s="43">
         <v>382</v>
       </c>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="85"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="26"/>
-      <c r="W25" s="82"/>
-      <c r="X25" s="26"/>
-      <c r="Y25" s="26"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="26"/>
-      <c r="AB25" s="26"/>
-      <c r="AC25" s="26"/>
-      <c r="AD25" s="26"/>
-      <c r="AE25" s="26"/>
-      <c r="AF25" s="26"/>
-      <c r="AG25" s="26"/>
-      <c r="AH25" s="129"/>
-    </row>
-    <row r="26" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH25" s="124"/>
+    </row>
+    <row r="26" spans="2:34" ht="15" thickBot="1">
       <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="131">
+      <c r="D26" s="126">
         <f t="array" ref="D26:E29">LINEST(K24:K29,L24:L29,TRUE,TRUE)</f>
-        <v>6.7252740680271748</v>
-      </c>
-      <c r="E26" s="132">
-        <v>174.9773679730506</v>
-      </c>
-      <c r="F26" s="26"/>
+        <v>6.7443407227222565</v>
+      </c>
+      <c r="E26" s="127">
+        <v>154.27188891012838</v>
+      </c>
       <c r="G26" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H26" s="21">
         <v>13</v>
@@ -9222,266 +8811,145 @@
       <c r="I26" s="21">
         <v>26.98</v>
       </c>
-      <c r="J26" s="39">
+      <c r="J26" s="38">
         <f t="shared" si="2"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K26" s="52">
-        <f t="shared" si="3"/>
-        <v>3025.1570117547149</v>
+      <c r="K26" s="51">
+        <f>(3500-87.68)*J26</f>
+        <v>2949.3725069573857</v>
       </c>
       <c r="L26" s="23">
         <v>420</v>
       </c>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="85"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="82"/>
-      <c r="X26" s="26"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="26"/>
-      <c r="AC26" s="26"/>
-      <c r="AD26" s="26"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="26"/>
-      <c r="AG26" s="26"/>
-      <c r="AH26" s="129"/>
-    </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH26" s="124"/>
+    </row>
+    <row r="27" spans="2:34">
       <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
       <c r="D27" s="25">
-        <v>0.13109567423964927</v>
-      </c>
-      <c r="E27" s="129">
-        <v>55.876727831054865</v>
-      </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="28">
+        <v>0.18295260319507423</v>
+      </c>
+      <c r="E27" s="124">
+        <v>77.979634904095917</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="27">
         <v>14</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="27">
         <v>28.09</v>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="36">
         <f t="shared" si="2"/>
         <v>0.86932910407021868</v>
       </c>
-      <c r="K27" s="53">
+      <c r="K27" s="52">
         <f t="shared" si="3"/>
         <v>3042.6518642457654</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="28">
         <v>426</v>
       </c>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="85"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="82"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
-      <c r="AD27" s="26"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="26"/>
-      <c r="AG27" s="26"/>
-      <c r="AH27" s="129"/>
-    </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH27" s="124"/>
+    </row>
+    <row r="28" spans="2:34">
       <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
       <c r="D28" s="25">
-        <v>0.99848240057289417</v>
-      </c>
-      <c r="E28" s="129">
-        <v>15.462344374388723</v>
-      </c>
-      <c r="F28" s="26"/>
-      <c r="G28" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="30">
+        <v>0.99706517829788954</v>
+      </c>
+      <c r="E28" s="124">
+        <v>21.578714715039371</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="29">
         <v>50</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="29">
         <v>116</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="30">
         <f>((SQRT(1-(1/I28)^2*SIN(RADIANS(165))^2)+1/I28*COS(RADIANS(165)))/(1+1/I28))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K28" s="54">
+      <c r="K28" s="53">
         <f t="shared" si="3"/>
         <v>3383.3516889668922</v>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="34">
         <v>477</v>
       </c>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="85"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="82"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="26"/>
-      <c r="AD28" s="26"/>
-      <c r="AE28" s="26"/>
-      <c r="AF28" s="26"/>
-      <c r="AG28" s="26"/>
-      <c r="AH28" s="129"/>
-    </row>
-    <row r="29" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH28" s="124"/>
+    </row>
+    <row r="29" spans="2:34" ht="15" thickBot="1">
       <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="61">
-        <v>2631.7416381135326</v>
-      </c>
-      <c r="E29" s="130">
+      <c r="D29" s="60">
+        <v>1358.9448075580581</v>
+      </c>
+      <c r="E29" s="125">
         <v>4</v>
       </c>
-      <c r="F29" s="26"/>
-      <c r="G29" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="34">
+      <c r="G29" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="33">
         <v>78</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="33">
         <v>195.1</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="37">
         <f>((SQRT(1-(1/I29)^2*SIN(RADIANS(165))^2)+1/I29*COS(RADIANS(165)))/(1+1/I29))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K29" s="55">
+      <c r="K29" s="54">
         <f t="shared" si="3"/>
         <v>3430.1698612157625</v>
       </c>
-      <c r="L29" s="36">
+      <c r="L29" s="35">
         <v>486</v>
       </c>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="85"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="82"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
-      <c r="AD29" s="26"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="26"/>
-      <c r="AG29" s="26"/>
-      <c r="AH29" s="129"/>
-    </row>
-    <row r="30" spans="2:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH29" s="124"/>
+    </row>
+    <row r="30" spans="2:34" ht="44.1" thickBot="1">
       <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
       <c r="M30" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R30" s="26"/>
-      <c r="S30" s="85"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="26"/>
-      <c r="W30" s="82"/>
-      <c r="X30" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y30" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z30" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB30" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD30" s="26"/>
-      <c r="AE30" s="26"/>
-      <c r="AF30" s="26"/>
-      <c r="AG30" s="26"/>
-      <c r="AH30" s="129"/>
-    </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH30" s="124"/>
+    </row>
+    <row r="31" spans="2:34">
       <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
       <c r="M31" s="4">
         <v>43.69</v>
       </c>
@@ -9500,625 +8968,386 @@
         <f>(($J$28/COS(RADIANS(0))*$N$31)+(1/COS(RADIANS(180-165))*$P$31))</f>
         <v>64.633240896229239</v>
       </c>
-      <c r="R31" s="26"/>
-      <c r="S31" s="85"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="82"/>
-      <c r="X31" s="26"/>
       <c r="Y31" s="17">
-        <v>75.7</v>
+        <v>75.239999999999995</v>
       </c>
       <c r="Z31" s="11">
         <f>Y31*$E$1/10</f>
-        <v>20.431429999999999</v>
+        <v>20.307275999999998</v>
       </c>
       <c r="AA31" s="17">
-        <v>82.01</v>
+        <v>83.51</v>
       </c>
       <c r="AB31" s="4">
         <f>AA31*$E$1/10</f>
-        <v>22.134498999999998</v>
+        <v>22.539349000000001</v>
       </c>
       <c r="AC31" s="10">
         <f>(($J$26/COS(RADIANS(0))*Z31)+(1/COS(RADIANS(180-165))*AB31))</f>
-        <v>40.574829215632406</v>
-      </c>
-      <c r="AD31" s="26"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="26"/>
-      <c r="AG31" s="26"/>
-      <c r="AH31" s="129"/>
-    </row>
-    <row r="32" spans="2:34" x14ac:dyDescent="0.35">
+        <v>40.886650679089321</v>
+      </c>
+      <c r="AH31" s="124"/>
+    </row>
+    <row r="32" spans="2:34">
       <c r="B32" s="25"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="85"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="82"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="26"/>
-      <c r="AD32" s="26"/>
-      <c r="AE32" s="26"/>
-      <c r="AF32" s="26"/>
-      <c r="AG32" s="26"/>
-      <c r="AH32" s="129"/>
-    </row>
-    <row r="33" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH32" s="124"/>
+    </row>
+    <row r="33" spans="2:34" ht="15" thickBot="1">
       <c r="B33" s="25"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="85"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="82"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="26"/>
-      <c r="AD33" s="26"/>
-      <c r="AE33" s="26"/>
-      <c r="AF33" s="26"/>
-      <c r="AG33" s="26"/>
-      <c r="AH33" s="129"/>
-    </row>
-    <row r="34" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH33" s="124"/>
+    </row>
+    <row r="34" spans="2:34" ht="29.45" thickBot="1">
       <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
       <c r="M34" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N34" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q34" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="R34" s="69"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="N34" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O34" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P34" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q34" s="104" t="s">
+      <c r="U34" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="V34" s="93"/>
+      <c r="W34" s="94"/>
+      <c r="Z34" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC34" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD34" s="72"/>
+      <c r="AE34" s="72"/>
+      <c r="AF34" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="R34" s="70"/>
-      <c r="S34" s="86"/>
-      <c r="T34" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U34" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="V34" s="98"/>
-      <c r="W34" s="99"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA34" s="6" t="s">
+      <c r="AH34" s="124"/>
+    </row>
+    <row r="35" spans="2:34" ht="15" thickBot="1">
+      <c r="B35" s="25"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="64">
+        <v>477</v>
+      </c>
+      <c r="O35" s="65">
+        <v>464</v>
+      </c>
+      <c r="P35" s="98">
+        <f>(N35-O35)*D26</f>
+        <v>87.676429395389334</v>
+      </c>
+      <c r="Q35" s="104">
+        <f>P35*10^3/Q31</f>
+        <v>1356.522250464845</v>
+      </c>
+      <c r="R35" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S35" s="106">
+        <f>Q35/D26*D27</f>
+        <v>36.798152290622987</v>
+      </c>
+      <c r="T35" s="107">
+        <v>1387</v>
+      </c>
+      <c r="U35" s="108">
+        <v>1361</v>
+      </c>
+      <c r="V35" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W35" s="110">
         <v>21</v>
       </c>
-      <c r="AB34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC34" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD34" s="73"/>
-      <c r="AE34" s="73"/>
-      <c r="AF34" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG34" s="26"/>
-      <c r="AH34" s="129"/>
-    </row>
-    <row r="35" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="65">
-        <v>477</v>
-      </c>
-      <c r="O35" s="66">
-        <v>464</v>
-      </c>
-      <c r="P35" s="103">
-        <f>(N35-O35)*D26</f>
-        <v>87.428562884353269</v>
-      </c>
-      <c r="Q35" s="109">
-        <f>P35*10^3/Q31</f>
-        <v>1352.6872809104941</v>
-      </c>
-      <c r="R35" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S35" s="111">
-        <f>Q35/D26*D27</f>
-        <v>26.36791442737119</v>
-      </c>
-      <c r="T35" s="112">
-        <v>1387</v>
-      </c>
-      <c r="U35" s="113">
-        <v>1361</v>
-      </c>
-      <c r="V35" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W35" s="115">
-        <v>21</v>
-      </c>
-      <c r="X35" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="116">
+      <c r="X35" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z35" s="111">
         <v>414</v>
       </c>
       <c r="AA35" s="16">
         <v>407</v>
       </c>
-      <c r="AB35" s="71">
+      <c r="AB35" s="70">
         <f>(Z35-AA35)*D26</f>
-        <v>47.076918476190222</v>
-      </c>
-      <c r="AC35" s="117">
+        <v>47.210385059055795</v>
+      </c>
+      <c r="AC35" s="112">
         <f>AB35*10^3/AC31</f>
-        <v>1160.2493315745796</v>
-      </c>
-      <c r="AD35" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE35" s="122">
+        <v>1154.6650135174957</v>
+      </c>
+      <c r="AD35" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE35" s="117">
         <f>AC35/D26*D27</f>
-        <v>22.616724146900197</v>
-      </c>
-      <c r="AF35" s="123">
+        <v>31.322404772580022</v>
+      </c>
+      <c r="AF35" s="118">
         <v>2.4900000000000002</v>
       </c>
-      <c r="AG35" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH35" s="129"/>
-    </row>
-    <row r="36" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG35" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH35" s="124"/>
+    </row>
+    <row r="36" spans="2:34" ht="15" thickBot="1">
       <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="107"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="108"/>
-      <c r="T36" s="100"/>
-      <c r="U36" s="100"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="105"/>
-      <c r="X36" s="26"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="69"/>
-      <c r="AD36" s="68"/>
-      <c r="AE36" s="87"/>
-      <c r="AF36" s="78"/>
-      <c r="AG36" s="26"/>
-      <c r="AH36" s="129"/>
-    </row>
-    <row r="37" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q36" s="102"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="95"/>
+      <c r="U36" s="95"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="100"/>
+      <c r="AC36" s="68"/>
+      <c r="AD36" s="67"/>
+      <c r="AE36" s="83"/>
+      <c r="AF36" s="76"/>
+      <c r="AH36" s="124"/>
+    </row>
+    <row r="37" spans="2:34" ht="15" thickBot="1">
       <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="94">
+      <c r="Q37" s="89">
         <f>Q35*$B$1*10^(-7)*10^3</f>
-        <v>0.98881440234557116</v>
-      </c>
-      <c r="R37" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S37" s="93">
+        <v>0.99161776508980159</v>
+      </c>
+      <c r="R37" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S37" s="88">
         <f>S35*$B$1*10^(-7)*10^3</f>
-        <v>1.9274945446408339E-2</v>
-      </c>
-      <c r="T37" s="79">
+        <v>2.6899449324445403E-2</v>
+      </c>
+      <c r="T37" s="131">
         <f>T35*$B$1*10^(-7)*10^3</f>
         <v>1.0138969999999998</v>
       </c>
-      <c r="U37" s="95">
+      <c r="U37" s="90">
         <f>U35*$B$1*10^(-7)*10^3</f>
         <v>0.99489099999999997</v>
       </c>
-      <c r="V37" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W37" s="106">
+      <c r="V37" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W37" s="101">
         <f>W35*$B$1*10^(-7)*10^3</f>
         <v>1.5351E-2</v>
       </c>
-      <c r="X37" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="118">
+      <c r="X37" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC37" s="113">
         <f>AC35*$E$1/10</f>
-        <v>313.15129459197902</v>
-      </c>
-      <c r="AD37" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE37" s="120">
+        <v>311.64408714837208</v>
+      </c>
+      <c r="AD37" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE37" s="115">
         <f>AE35*$E$1*10^(-7)*10^6</f>
-        <v>6.104253847248363</v>
-      </c>
-      <c r="AF37" s="124">
+        <v>8.4539170481193473</v>
+      </c>
+      <c r="AF37" s="119">
         <f>AF35*$E$1/10</f>
         <v>0.67205099999999995</v>
       </c>
-      <c r="AG37" s="67" t="s">
+      <c r="AG37" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH37" s="129"/>
-    </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH37" s="124"/>
+    </row>
+    <row r="38" spans="2:34">
       <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="85"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="74"/>
-      <c r="V38" s="74"/>
-      <c r="W38" s="89"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
-      <c r="AA38" s="26"/>
-      <c r="AB38" s="26"/>
-      <c r="AC38" s="26"/>
-      <c r="AD38" s="26"/>
-      <c r="AE38" s="26"/>
-      <c r="AF38" s="26"/>
-      <c r="AG38" s="26"/>
-      <c r="AH38" s="129"/>
-    </row>
-    <row r="39" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="61"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="62"/>
-      <c r="O39" s="62"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="88"/>
-      <c r="T39" s="62"/>
-      <c r="U39" s="75"/>
-      <c r="V39" s="75"/>
-      <c r="W39" s="90"/>
-      <c r="X39" s="62"/>
-      <c r="Y39" s="62"/>
-      <c r="Z39" s="62"/>
-      <c r="AA39" s="62"/>
-      <c r="AB39" s="62"/>
-      <c r="AC39" s="62"/>
-      <c r="AD39" s="62"/>
-      <c r="AE39" s="62"/>
-      <c r="AF39" s="62"/>
-      <c r="AG39" s="62"/>
-      <c r="AH39" s="130"/>
-    </row>
-    <row r="40" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="91"/>
-      <c r="AD40" s="26"/>
-      <c r="AF40" s="26"/>
-    </row>
-    <row r="41" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="59"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="60"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60"/>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="84"/>
-      <c r="T41" s="60"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="60"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="60"/>
-      <c r="Y41" s="60"/>
-      <c r="Z41" s="60"/>
-      <c r="AA41" s="60"/>
-      <c r="AB41" s="60"/>
-      <c r="AC41" s="60"/>
-      <c r="AD41" s="60"/>
-      <c r="AE41" s="60"/>
-      <c r="AF41" s="60"/>
-      <c r="AG41" s="60"/>
-      <c r="AH41" s="128"/>
-    </row>
-    <row r="42" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U38" s="73"/>
+      <c r="V38" s="73"/>
+      <c r="W38" s="85"/>
+      <c r="AH38" s="124"/>
+    </row>
+    <row r="39" spans="2:34" ht="15" thickBot="1">
+      <c r="B39" s="60"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="61"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="84"/>
+      <c r="T39" s="61"/>
+      <c r="U39" s="74"/>
+      <c r="V39" s="74"/>
+      <c r="W39" s="86"/>
+      <c r="X39" s="61"/>
+      <c r="Y39" s="61"/>
+      <c r="Z39" s="61"/>
+      <c r="AA39" s="61"/>
+      <c r="AB39" s="61"/>
+      <c r="AC39" s="61"/>
+      <c r="AD39" s="61"/>
+      <c r="AE39" s="61"/>
+      <c r="AF39" s="61"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="125"/>
+    </row>
+    <row r="40" spans="2:34" ht="15" thickBot="1">
+      <c r="U40" s="73"/>
+      <c r="V40" s="73"/>
+      <c r="W40" s="85"/>
+    </row>
+    <row r="41" spans="2:34" ht="15" thickBot="1">
+      <c r="B41" s="58"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
+      <c r="R41" s="59"/>
+      <c r="S41" s="81"/>
+      <c r="T41" s="59"/>
+      <c r="U41" s="59"/>
+      <c r="V41" s="59"/>
+      <c r="W41" s="79"/>
+      <c r="X41" s="59"/>
+      <c r="Y41" s="59"/>
+      <c r="Z41" s="59"/>
+      <c r="AA41" s="59"/>
+      <c r="AB41" s="59"/>
+      <c r="AC41" s="59"/>
+      <c r="AD41" s="59"/>
+      <c r="AE41" s="59"/>
+      <c r="AF41" s="59"/>
+      <c r="AG41" s="59"/>
+      <c r="AH41" s="123"/>
+    </row>
+    <row r="42" spans="2:34" ht="29.45" thickBot="1">
       <c r="B42" s="25"/>
-      <c r="C42" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="57">
+      <c r="C42" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="56">
         <v>3.9</v>
       </c>
-      <c r="E42" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="26"/>
+      <c r="E42" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G42" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L42" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH42" s="124"/>
+    </row>
+    <row r="43" spans="2:34">
+      <c r="B43" s="25"/>
+      <c r="G43" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="45">
         <v>6</v>
       </c>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="85"/>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="26"/>
-      <c r="W42" s="82"/>
-      <c r="X42" s="26"/>
-      <c r="Y42" s="26"/>
-      <c r="Z42" s="26"/>
-      <c r="AA42" s="26"/>
-      <c r="AB42" s="26"/>
-      <c r="AC42" s="26"/>
-      <c r="AD42" s="26"/>
-      <c r="AE42" s="26"/>
-      <c r="AF42" s="26"/>
-      <c r="AG42" s="26"/>
-      <c r="AH42" s="129"/>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.35">
-      <c r="B43" s="25"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="46">
-        <v>6</v>
-      </c>
-      <c r="I43" s="46">
+      <c r="I43" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J43" s="47">
+      <c r="J43" s="46">
         <f>((SQRT(1-(1/I43)^2*SIN(RADIANS(165))^2)+1/I43*COS(RADIANS(165)))/(1+1/I43))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K43" s="50">
+      <c r="K43" s="49">
         <f>$D$42*1000*J43</f>
         <v>2809.0610536591207</v>
       </c>
-      <c r="L43" s="48">
+      <c r="L43" s="47">
         <v>300</v>
       </c>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="85"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="26"/>
-      <c r="W43" s="82"/>
-      <c r="X43" s="26"/>
-      <c r="Y43" s="26"/>
-      <c r="Z43" s="26"/>
-      <c r="AA43" s="26"/>
-      <c r="AB43" s="26"/>
-      <c r="AC43" s="26"/>
-      <c r="AD43" s="26"/>
-      <c r="AE43" s="26"/>
-      <c r="AF43" s="26"/>
-      <c r="AG43" s="26"/>
-      <c r="AH43" s="129"/>
-    </row>
-    <row r="44" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH43" s="124"/>
+    </row>
+    <row r="44" spans="2:34" ht="15" thickBot="1">
       <c r="B44" s="25"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" s="41">
+      <c r="G44" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="40">
         <v>8</v>
       </c>
-      <c r="I44" s="42">
+      <c r="I44" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J44" s="43">
+      <c r="J44" s="42">
         <f t="shared" ref="J44:J46" si="4">((SQRT(1-(1/I44)^2*SIN(RADIANS(165))^2)+1/I44*COS(RADIANS(165)))/(1+1/I44))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K44" s="51">
+      <c r="K44" s="50">
         <f t="shared" ref="K44:K48" si="5">$D$42*1000*J44</f>
         <v>3049.2461563973534</v>
       </c>
-      <c r="L44" s="44">
+      <c r="L44" s="43">
         <v>328</v>
       </c>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="85"/>
-      <c r="T44" s="26"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="26"/>
-      <c r="W44" s="82"/>
-      <c r="X44" s="26"/>
-      <c r="Y44" s="26"/>
-      <c r="Z44" s="26"/>
-      <c r="AA44" s="26"/>
-      <c r="AB44" s="26"/>
-      <c r="AC44" s="26"/>
-      <c r="AD44" s="26"/>
-      <c r="AE44" s="26"/>
-      <c r="AF44" s="26"/>
-      <c r="AG44" s="26"/>
-      <c r="AH44" s="129"/>
-    </row>
-    <row r="45" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH44" s="124"/>
+    </row>
+    <row r="45" spans="2:34" ht="15" thickBot="1">
       <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="131">
+      <c r="D45" s="126">
         <f t="array" ref="D45:E48">LINEST(K43:K48,L43:L48,TRUE,TRUE)</f>
-        <v>8.6163917435189159</v>
-      </c>
-      <c r="E45" s="132">
-        <v>240.16337861504917</v>
-      </c>
-      <c r="F45" s="26"/>
+        <v>8.6587074818560179</v>
+      </c>
+      <c r="E45" s="127">
+        <v>213.57302567162697</v>
+      </c>
       <c r="G45" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H45" s="21">
         <v>13</v>
@@ -10126,266 +9355,145 @@
       <c r="I45" s="21">
         <v>26.98</v>
       </c>
-      <c r="J45" s="39">
+      <c r="J45" s="38">
         <f t="shared" si="4"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K45" s="52">
-        <f t="shared" si="5"/>
-        <v>3370.8892416695394</v>
+      <c r="K45" s="51">
+        <f>(3900-77.93)*J45</f>
+        <v>3303.5319599763839</v>
       </c>
       <c r="L45" s="23">
         <v>356.5</v>
       </c>
-      <c r="M45" s="26"/>
-      <c r="N45" s="26"/>
-      <c r="O45" s="26"/>
-      <c r="P45" s="26"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="26"/>
-      <c r="S45" s="85"/>
-      <c r="T45" s="26"/>
-      <c r="U45" s="26"/>
-      <c r="V45" s="26"/>
-      <c r="W45" s="82"/>
-      <c r="X45" s="26"/>
-      <c r="Y45" s="26"/>
-      <c r="Z45" s="26"/>
-      <c r="AA45" s="26"/>
-      <c r="AB45" s="26"/>
-      <c r="AC45" s="26"/>
-      <c r="AD45" s="26"/>
-      <c r="AE45" s="26"/>
-      <c r="AF45" s="26"/>
-      <c r="AG45" s="26"/>
-      <c r="AH45" s="129"/>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH45" s="124"/>
+    </row>
+    <row r="46" spans="2:34">
       <c r="B46" s="25"/>
-      <c r="C46" s="26"/>
       <c r="D46" s="25">
-        <v>0.32518562881215768</v>
-      </c>
-      <c r="E46" s="129">
-        <v>118.8490265802717</v>
-      </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="28">
+        <v>7.7047909861678518E-2</v>
+      </c>
+      <c r="E46" s="124">
+        <v>28.159513446378519</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="27">
         <v>14</v>
       </c>
-      <c r="I46" s="28">
+      <c r="I46" s="27">
         <v>28.09</v>
       </c>
-      <c r="J46" s="37">
+      <c r="J46" s="36">
         <f t="shared" si="4"/>
         <v>0.86932910407021868</v>
       </c>
-      <c r="K46" s="53">
+      <c r="K46" s="52">
         <f t="shared" si="5"/>
         <v>3390.3835058738528</v>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="28">
         <v>366</v>
       </c>
-      <c r="M46" s="26"/>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="26"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="85"/>
-      <c r="T46" s="26"/>
-      <c r="U46" s="26"/>
-      <c r="V46" s="26"/>
-      <c r="W46" s="82"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="26"/>
-      <c r="AC46" s="26"/>
-      <c r="AD46" s="26"/>
-      <c r="AE46" s="26"/>
-      <c r="AF46" s="26"/>
-      <c r="AG46" s="26"/>
-      <c r="AH46" s="129"/>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH46" s="124"/>
+    </row>
+    <row r="47" spans="2:34">
       <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
       <c r="D47" s="25">
-        <v>0.99433494007238665</v>
-      </c>
-      <c r="E47" s="129">
-        <v>33.288603894552338</v>
-      </c>
-      <c r="F47" s="26"/>
-      <c r="G47" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47" s="30">
+        <v>0.99968338021421288</v>
+      </c>
+      <c r="E47" s="124">
+        <v>7.8872407789279855</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="29">
         <v>50</v>
       </c>
-      <c r="I47" s="30">
+      <c r="I47" s="29">
         <v>116</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="30">
         <f>((SQRT(1-(1/I47)^2*SIN(RADIANS(165))^2)+1/I47*COS(RADIANS(165)))/(1+1/I47))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K47" s="54">
+      <c r="K47" s="53">
         <f t="shared" si="5"/>
         <v>3770.0204534202512</v>
       </c>
-      <c r="L47" s="35">
+      <c r="L47" s="34">
         <v>410</v>
       </c>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="26"/>
-      <c r="S47" s="85"/>
-      <c r="T47" s="26"/>
-      <c r="U47" s="26"/>
-      <c r="V47" s="26"/>
-      <c r="W47" s="82"/>
-      <c r="X47" s="26"/>
-      <c r="Y47" s="26"/>
-      <c r="Z47" s="26"/>
-      <c r="AA47" s="26"/>
-      <c r="AB47" s="26"/>
-      <c r="AC47" s="26"/>
-      <c r="AD47" s="26"/>
-      <c r="AE47" s="26"/>
-      <c r="AF47" s="26"/>
-      <c r="AG47" s="26"/>
-      <c r="AH47" s="129"/>
-    </row>
-    <row r="48" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH47" s="124"/>
+    </row>
+    <row r="48" spans="2:34" ht="15" thickBot="1">
       <c r="B48" s="25"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="61">
-        <v>702.08255713282642</v>
-      </c>
-      <c r="E48" s="130">
+      <c r="D48" s="60">
+        <v>12629.449264885958</v>
+      </c>
+      <c r="E48" s="125">
         <v>4</v>
       </c>
-      <c r="F48" s="26"/>
-      <c r="G48" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H48" s="34">
+      <c r="G48" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="33">
         <v>78</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="33">
         <v>195.1</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="37">
         <f>((SQRT(1-(1/I48)^2*SIN(RADIANS(165))^2)+1/I48*COS(RADIANS(165)))/(1+1/I48))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K48" s="55">
+      <c r="K48" s="54">
         <f t="shared" si="5"/>
         <v>3822.1892739261352</v>
       </c>
-      <c r="L48" s="36">
+      <c r="L48" s="35">
         <v>418</v>
       </c>
-      <c r="M48" s="26"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="85"/>
-      <c r="T48" s="26"/>
-      <c r="U48" s="26"/>
-      <c r="V48" s="26"/>
-      <c r="W48" s="82"/>
-      <c r="X48" s="26"/>
-      <c r="Y48" s="26"/>
-      <c r="Z48" s="26"/>
-      <c r="AA48" s="26"/>
-      <c r="AB48" s="26"/>
-      <c r="AC48" s="26"/>
-      <c r="AD48" s="26"/>
-      <c r="AE48" s="26"/>
-      <c r="AF48" s="26"/>
-      <c r="AG48" s="26"/>
-      <c r="AH48" s="129"/>
-    </row>
-    <row r="49" spans="2:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH48" s="124"/>
+    </row>
+    <row r="49" spans="2:34" ht="44.1" thickBot="1">
       <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
       <c r="M49" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R49" s="26"/>
-      <c r="S49" s="85"/>
-      <c r="T49" s="26"/>
-      <c r="U49" s="26"/>
-      <c r="V49" s="26"/>
-      <c r="W49" s="82"/>
-      <c r="X49" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD49" s="26"/>
-      <c r="AE49" s="26"/>
-      <c r="AF49" s="26"/>
-      <c r="AG49" s="26"/>
-      <c r="AH49" s="129"/>
-    </row>
-    <row r="50" spans="2:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH49" s="124"/>
+    </row>
+    <row r="50" spans="2:34">
       <c r="B50" s="25"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
       <c r="M50" s="4">
         <v>40.86</v>
       </c>
@@ -10404,625 +9512,386 @@
         <f>(($J$47/COS(RADIANS(0))*$N$50)+(1/COS(RADIANS(180-165))*$P$50))</f>
         <v>60.453911476416494</v>
       </c>
-      <c r="R50" s="26"/>
-      <c r="S50" s="85"/>
-      <c r="T50" s="26"/>
-      <c r="U50" s="26"/>
-      <c r="V50" s="26"/>
-      <c r="W50" s="82"/>
-      <c r="X50" s="26"/>
       <c r="Y50" s="17">
-        <v>70.010000000000005</v>
+        <v>69.319999999999993</v>
       </c>
       <c r="Z50" s="11">
         <f>Y50*$E$1/10</f>
-        <v>18.895699</v>
+        <v>18.709467999999998</v>
       </c>
       <c r="AA50" s="17">
-        <v>75.900000000000006</v>
+        <v>77</v>
       </c>
       <c r="AB50" s="4">
         <f>AA50*$E$1/10</f>
-        <v>20.485410000000002</v>
+        <v>20.782299999999999</v>
       </c>
       <c r="AC50" s="10">
         <f>(($J$45/COS(RADIANS(0))*Z50)+(1/COS(RADIANS(180-165))*AB50))</f>
-        <v>37.54018739660782</v>
-      </c>
-      <c r="AD50" s="26"/>
-      <c r="AE50" s="26"/>
-      <c r="AF50" s="26"/>
-      <c r="AG50" s="26"/>
-      <c r="AH50" s="129"/>
-    </row>
-    <row r="51" spans="2:34" x14ac:dyDescent="0.35">
+        <v>37.686585394536593</v>
+      </c>
+      <c r="AH50" s="124"/>
+    </row>
+    <row r="51" spans="2:34">
       <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
-      <c r="P51" s="26"/>
-      <c r="Q51" s="26"/>
-      <c r="R51" s="26"/>
-      <c r="S51" s="85"/>
-      <c r="T51" s="26"/>
-      <c r="U51" s="26"/>
-      <c r="V51" s="26"/>
-      <c r="W51" s="82"/>
-      <c r="X51" s="26"/>
-      <c r="Y51" s="26"/>
-      <c r="Z51" s="26"/>
-      <c r="AA51" s="26"/>
-      <c r="AB51" s="26"/>
-      <c r="AC51" s="26"/>
-      <c r="AD51" s="26"/>
-      <c r="AE51" s="26"/>
-      <c r="AF51" s="26"/>
-      <c r="AG51" s="26"/>
-      <c r="AH51" s="129"/>
-    </row>
-    <row r="52" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH51" s="124"/>
+    </row>
+    <row r="52" spans="2:34" ht="15" thickBot="1">
       <c r="B52" s="25"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26"/>
-      <c r="O52" s="26"/>
-      <c r="P52" s="26"/>
-      <c r="Q52" s="26"/>
-      <c r="R52" s="26"/>
-      <c r="S52" s="85"/>
-      <c r="T52" s="26"/>
-      <c r="U52" s="26"/>
-      <c r="V52" s="26"/>
-      <c r="W52" s="82"/>
-      <c r="X52" s="26"/>
-      <c r="Y52" s="26"/>
-      <c r="Z52" s="26"/>
-      <c r="AA52" s="26"/>
-      <c r="AB52" s="26"/>
-      <c r="AC52" s="26"/>
-      <c r="AD52" s="26"/>
-      <c r="AE52" s="26"/>
-      <c r="AF52" s="26"/>
-      <c r="AG52" s="26"/>
-      <c r="AH52" s="129"/>
-    </row>
-    <row r="53" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH52" s="124"/>
+    </row>
+    <row r="53" spans="2:34" ht="29.45" thickBot="1">
       <c r="B53" s="25"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
       <c r="M53" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N53" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P53" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q53" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="R53" s="69"/>
+      <c r="S53" s="82"/>
+      <c r="T53" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="U53" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="N53" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O53" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P53" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q53" s="104" t="s">
+      <c r="V53" s="93"/>
+      <c r="W53" s="94"/>
+      <c r="Z53" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC53" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD53" s="72"/>
+      <c r="AE53" s="72"/>
+      <c r="AF53" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="R53" s="70"/>
-      <c r="S53" s="86"/>
-      <c r="T53" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U53" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="V53" s="98"/>
-      <c r="W53" s="99"/>
-      <c r="X53" s="26"/>
-      <c r="Y53" s="26"/>
-      <c r="Z53" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA53" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB53" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC53" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD53" s="73"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG53" s="26"/>
-      <c r="AH53" s="129"/>
-    </row>
-    <row r="54" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH53" s="124"/>
+    </row>
+    <row r="54" spans="2:34" ht="15" thickBot="1">
       <c r="B54" s="25"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
       <c r="M54" s="18"/>
-      <c r="N54" s="65">
+      <c r="N54" s="64">
         <v>410</v>
       </c>
-      <c r="O54" s="66">
+      <c r="O54" s="65">
         <v>401</v>
       </c>
-      <c r="P54" s="103">
+      <c r="P54" s="98">
         <f>(N54-O54)*D45</f>
-        <v>77.547525691670245</v>
-      </c>
-      <c r="Q54" s="109">
+        <v>77.928367336704156</v>
+      </c>
+      <c r="Q54" s="104">
         <f>P54*10^3/Q50</f>
-        <v>1282.7544785406003</v>
-      </c>
-      <c r="R54" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S54" s="111">
+        <v>1289.0541808383164</v>
+      </c>
+      <c r="R54" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S54" s="106">
         <f>Q54/D45*D46</f>
-        <v>48.411601298141555</v>
-      </c>
-      <c r="T54" s="112">
+        <v>11.470410628857641</v>
+      </c>
+      <c r="T54" s="107">
         <v>1438</v>
       </c>
-      <c r="U54" s="113">
+      <c r="U54" s="108">
         <v>1439</v>
       </c>
-      <c r="V54" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W54" s="115">
+      <c r="V54" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W54" s="110">
         <v>77</v>
       </c>
-      <c r="X54" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y54" s="26"/>
-      <c r="Z54" s="116">
+      <c r="X54" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z54" s="111">
         <v>356.5</v>
       </c>
       <c r="AA54" s="16">
         <v>352.5</v>
       </c>
-      <c r="AB54" s="71">
+      <c r="AB54" s="70">
         <f>(Z54-AA54)*D45</f>
-        <v>34.465566974075664</v>
-      </c>
-      <c r="AC54" s="117">
+        <v>34.634829927424072</v>
+      </c>
+      <c r="AC54" s="112">
         <f>AB54*10^3/AC50</f>
-        <v>918.09789359735635</v>
-      </c>
-      <c r="AD54" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE54" s="122">
+        <v>919.02276539081379</v>
+      </c>
+      <c r="AD54" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE54" s="117">
         <f>AC54/D45*D46</f>
-        <v>34.649334631882191</v>
-      </c>
-      <c r="AF54" s="123">
+        <v>8.1777543977595943</v>
+      </c>
+      <c r="AF54" s="118">
         <v>16.93</v>
       </c>
-      <c r="AG54" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH54" s="129"/>
-    </row>
-    <row r="55" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG54" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH54" s="124"/>
+    </row>
+    <row r="55" spans="2:34" ht="15" thickBot="1">
       <c r="B55" s="25"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="26"/>
-      <c r="O55" s="26"/>
-      <c r="P55" s="26"/>
-      <c r="Q55" s="107"/>
-      <c r="R55" s="74"/>
-      <c r="S55" s="108"/>
-      <c r="T55" s="100"/>
-      <c r="U55" s="100"/>
-      <c r="V55" s="74"/>
-      <c r="W55" s="105"/>
-      <c r="X55" s="26"/>
-      <c r="Y55" s="26"/>
-      <c r="Z55" s="26"/>
-      <c r="AA55" s="26"/>
-      <c r="AB55" s="26"/>
-      <c r="AC55" s="69"/>
-      <c r="AD55" s="68"/>
-      <c r="AE55" s="87"/>
-      <c r="AF55" s="78"/>
-      <c r="AG55" s="26"/>
-      <c r="AH55" s="129"/>
-    </row>
-    <row r="56" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q55" s="102"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="103"/>
+      <c r="T55" s="95"/>
+      <c r="U55" s="95"/>
+      <c r="V55" s="73"/>
+      <c r="W55" s="100"/>
+      <c r="AC55" s="68"/>
+      <c r="AD55" s="67"/>
+      <c r="AE55" s="83"/>
+      <c r="AF55" s="76"/>
+      <c r="AH55" s="124"/>
+    </row>
+    <row r="56" spans="2:34" ht="15" thickBot="1">
       <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
-      <c r="P56" s="26"/>
-      <c r="Q56" s="94">
+      <c r="Q56" s="89">
         <f>Q54*$B$1*10^(-7)*10^3</f>
-        <v>0.93769352381317872</v>
-      </c>
-      <c r="R56" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S56" s="93">
+        <v>0.94229860619280914</v>
+      </c>
+      <c r="R56" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S56" s="88">
         <f>S54*$B$1*10^(-7)*10^3</f>
-        <v>3.5388880548941466E-2</v>
-      </c>
-      <c r="T56" s="79">
+        <v>8.3848701696949343E-3</v>
+      </c>
+      <c r="T56" s="131">
         <f>T54*$B$1*10^(-7)*10^3</f>
         <v>1.0511779999999997</v>
       </c>
-      <c r="U56" s="95">
+      <c r="U56" s="90">
         <f>U54*$B$1*10^(-7)*10^3</f>
         <v>1.051909</v>
       </c>
-      <c r="V56" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W56" s="106">
+      <c r="V56" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W56" s="101">
         <f>W54*$B$1*10^(-7)*10^3</f>
         <v>5.6286999999999997E-2</v>
       </c>
-      <c r="X56" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y56" s="26"/>
-      <c r="Z56" s="26"/>
-      <c r="AA56" s="26"/>
-      <c r="AB56" s="26"/>
-      <c r="AC56" s="118">
+      <c r="X56" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC56" s="113">
         <f>AC54*$E$1/10</f>
-        <v>247.79462148192647</v>
-      </c>
-      <c r="AD56" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE56" s="120">
+        <v>248.04424437898064</v>
+      </c>
+      <c r="AD56" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE56" s="115">
         <f>AE54*$E$1*10^(-7)*10^6</f>
-        <v>9.3518554171450017</v>
-      </c>
-      <c r="AF56" s="124">
+        <v>2.2071759119553138</v>
+      </c>
+      <c r="AF56" s="119">
         <f>AF54*$E$1/10</f>
         <v>4.569407</v>
       </c>
-      <c r="AG56" s="67" t="s">
+      <c r="AG56" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH56" s="129"/>
-    </row>
-    <row r="57" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH56" s="124"/>
+    </row>
+    <row r="57" spans="2:34">
       <c r="B57" s="25"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="26"/>
-      <c r="O57" s="26"/>
-      <c r="P57" s="26"/>
-      <c r="Q57" s="26"/>
-      <c r="R57" s="26"/>
-      <c r="S57" s="85"/>
-      <c r="T57" s="26"/>
-      <c r="U57" s="74"/>
-      <c r="V57" s="74"/>
-      <c r="W57" s="89"/>
-      <c r="X57" s="26"/>
-      <c r="Y57" s="26"/>
-      <c r="Z57" s="26"/>
-      <c r="AA57" s="26"/>
-      <c r="AB57" s="26"/>
-      <c r="AC57" s="26"/>
-      <c r="AD57" s="26"/>
-      <c r="AE57" s="26"/>
-      <c r="AF57" s="26"/>
-      <c r="AG57" s="26"/>
-      <c r="AH57" s="129"/>
-    </row>
-    <row r="58" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="61"/>
-      <c r="C58" s="62"/>
-      <c r="D58" s="62"/>
-      <c r="E58" s="62"/>
-      <c r="F58" s="62"/>
-      <c r="G58" s="62"/>
-      <c r="H58" s="62"/>
-      <c r="I58" s="62"/>
-      <c r="J58" s="62"/>
-      <c r="K58" s="62"/>
-      <c r="L58" s="62"/>
-      <c r="M58" s="62"/>
-      <c r="N58" s="62"/>
-      <c r="O58" s="62"/>
-      <c r="P58" s="62"/>
-      <c r="Q58" s="62"/>
-      <c r="R58" s="62"/>
-      <c r="S58" s="88"/>
-      <c r="T58" s="62"/>
-      <c r="U58" s="75"/>
-      <c r="V58" s="75"/>
-      <c r="W58" s="90"/>
-      <c r="X58" s="62"/>
-      <c r="Y58" s="62"/>
-      <c r="Z58" s="62"/>
-      <c r="AA58" s="62"/>
-      <c r="AB58" s="62"/>
-      <c r="AC58" s="62"/>
-      <c r="AD58" s="62"/>
-      <c r="AE58" s="62"/>
-      <c r="AF58" s="62"/>
-      <c r="AG58" s="62"/>
-      <c r="AH58" s="130"/>
-    </row>
-    <row r="59" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U59" s="77"/>
-      <c r="V59" s="77"/>
-      <c r="W59" s="91"/>
-      <c r="AD59" s="26"/>
-      <c r="AF59" s="26"/>
-    </row>
-    <row r="60" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="59"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="60"/>
-      <c r="H60" s="60"/>
-      <c r="I60" s="60"/>
-      <c r="J60" s="60"/>
-      <c r="K60" s="60"/>
-      <c r="L60" s="60"/>
-      <c r="M60" s="60"/>
-      <c r="N60" s="60"/>
-      <c r="O60" s="60"/>
-      <c r="P60" s="60"/>
-      <c r="Q60" s="60"/>
-      <c r="R60" s="60"/>
-      <c r="S60" s="84"/>
-      <c r="T60" s="60"/>
-      <c r="U60" s="60"/>
-      <c r="V60" s="60"/>
-      <c r="W60" s="81"/>
-      <c r="X60" s="60"/>
-      <c r="Y60" s="60"/>
-      <c r="Z60" s="60"/>
-      <c r="AA60" s="60"/>
-      <c r="AB60" s="60"/>
-      <c r="AC60" s="60"/>
-      <c r="AD60" s="60"/>
-      <c r="AE60" s="60"/>
-      <c r="AF60" s="60"/>
-      <c r="AG60" s="60"/>
-      <c r="AH60" s="128"/>
-    </row>
-    <row r="61" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U57" s="73"/>
+      <c r="V57" s="73"/>
+      <c r="W57" s="85"/>
+      <c r="AH57" s="124"/>
+    </row>
+    <row r="58" spans="2:34" ht="15" thickBot="1">
+      <c r="B58" s="60"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="61"/>
+      <c r="P58" s="61"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="61"/>
+      <c r="S58" s="84"/>
+      <c r="T58" s="61"/>
+      <c r="U58" s="74"/>
+      <c r="V58" s="74"/>
+      <c r="W58" s="86"/>
+      <c r="X58" s="61"/>
+      <c r="Y58" s="61"/>
+      <c r="Z58" s="61"/>
+      <c r="AA58" s="61"/>
+      <c r="AB58" s="61"/>
+      <c r="AC58" s="61"/>
+      <c r="AD58" s="61"/>
+      <c r="AE58" s="61"/>
+      <c r="AF58" s="61"/>
+      <c r="AG58" s="61"/>
+      <c r="AH58" s="125"/>
+    </row>
+    <row r="59" spans="2:34" ht="15" thickBot="1">
+      <c r="U59" s="73"/>
+      <c r="V59" s="73"/>
+      <c r="W59" s="85"/>
+    </row>
+    <row r="60" spans="2:34" ht="15" thickBot="1">
+      <c r="B60" s="58"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="59"/>
+      <c r="M60" s="59"/>
+      <c r="N60" s="59"/>
+      <c r="O60" s="59"/>
+      <c r="P60" s="59"/>
+      <c r="Q60" s="59"/>
+      <c r="R60" s="59"/>
+      <c r="S60" s="81"/>
+      <c r="T60" s="59"/>
+      <c r="U60" s="59"/>
+      <c r="V60" s="59"/>
+      <c r="W60" s="79"/>
+      <c r="X60" s="59"/>
+      <c r="Y60" s="59"/>
+      <c r="Z60" s="59"/>
+      <c r="AA60" s="59"/>
+      <c r="AB60" s="59"/>
+      <c r="AC60" s="59"/>
+      <c r="AD60" s="59"/>
+      <c r="AE60" s="59"/>
+      <c r="AF60" s="59"/>
+      <c r="AG60" s="59"/>
+      <c r="AH60" s="123"/>
+    </row>
+    <row r="61" spans="2:34" ht="29.45" thickBot="1">
       <c r="B61" s="25"/>
-      <c r="C61" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="57">
+      <c r="C61" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="56">
         <v>4.3</v>
       </c>
-      <c r="E61" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F61" s="26"/>
+      <c r="E61" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G61" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I61" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J61" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L61" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH61" s="124"/>
+    </row>
+    <row r="62" spans="2:34">
+      <c r="B62" s="25"/>
+      <c r="G62" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="45">
         <v>6</v>
       </c>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="85"/>
-      <c r="T61" s="26"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="26"/>
-      <c r="W61" s="82"/>
-      <c r="X61" s="26"/>
-      <c r="Y61" s="26"/>
-      <c r="Z61" s="26"/>
-      <c r="AA61" s="26"/>
-      <c r="AB61" s="26"/>
-      <c r="AC61" s="26"/>
-      <c r="AD61" s="26"/>
-      <c r="AE61" s="26"/>
-      <c r="AF61" s="26"/>
-      <c r="AG61" s="26"/>
-      <c r="AH61" s="129"/>
-    </row>
-    <row r="62" spans="2:34" x14ac:dyDescent="0.35">
-      <c r="B62" s="25"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H62" s="46">
-        <v>6</v>
-      </c>
-      <c r="I62" s="46">
+      <c r="I62" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J62" s="47">
+      <c r="J62" s="46">
         <f>((SQRT(1-(1/I62)^2*SIN(RADIANS(165))^2)+1/I62*COS(RADIANS(165)))/(1+1/I62))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="49">
         <f>$D$61*1000*J62</f>
         <v>3097.1698796754408</v>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="47">
         <v>334</v>
       </c>
-      <c r="M62" s="26"/>
-      <c r="N62" s="26"/>
-      <c r="O62" s="26"/>
-      <c r="P62" s="26"/>
-      <c r="Q62" s="26"/>
-      <c r="R62" s="26"/>
-      <c r="S62" s="85"/>
-      <c r="T62" s="26"/>
-      <c r="U62" s="26"/>
-      <c r="V62" s="26"/>
-      <c r="W62" s="82"/>
-      <c r="X62" s="26"/>
-      <c r="Y62" s="26"/>
-      <c r="Z62" s="26"/>
-      <c r="AA62" s="26"/>
-      <c r="AB62" s="26"/>
-      <c r="AC62" s="26"/>
-      <c r="AD62" s="26"/>
-      <c r="AE62" s="26"/>
-      <c r="AF62" s="26"/>
-      <c r="AG62" s="26"/>
-      <c r="AH62" s="129"/>
-    </row>
-    <row r="63" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH62" s="124"/>
+    </row>
+    <row r="63" spans="2:34" ht="15" thickBot="1">
       <c r="B63" s="25"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H63" s="41">
+      <c r="G63" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="40">
         <v>8</v>
       </c>
-      <c r="I63" s="42">
+      <c r="I63" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J63" s="43">
+      <c r="J63" s="42">
         <f t="shared" ref="J63:J65" si="6">((SQRT(1-(1/I63)^2*SIN(RADIANS(165))^2)+1/I63*COS(RADIANS(165)))/(1+1/I63))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K63" s="51">
+      <c r="K63" s="50">
         <f t="shared" ref="K63:K67" si="7">$D$61*1000*J63</f>
         <v>3361.9893519252869</v>
       </c>
-      <c r="L63" s="44">
+      <c r="L63" s="43">
         <v>364</v>
       </c>
-      <c r="M63" s="26"/>
-      <c r="N63" s="26"/>
-      <c r="O63" s="26"/>
-      <c r="P63" s="26"/>
-      <c r="Q63" s="26"/>
-      <c r="R63" s="26"/>
-      <c r="S63" s="85"/>
-      <c r="T63" s="26"/>
-      <c r="U63" s="26"/>
-      <c r="V63" s="26"/>
-      <c r="W63" s="82"/>
-      <c r="X63" s="26"/>
-      <c r="Y63" s="26"/>
-      <c r="Z63" s="26"/>
-      <c r="AA63" s="26"/>
-      <c r="AB63" s="26"/>
-      <c r="AC63" s="26"/>
-      <c r="AD63" s="26"/>
-      <c r="AE63" s="26"/>
-      <c r="AF63" s="26"/>
-      <c r="AG63" s="26"/>
-      <c r="AH63" s="129"/>
-    </row>
-    <row r="64" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH63" s="124"/>
+    </row>
+    <row r="64" spans="2:34" ht="15" thickBot="1">
       <c r="B64" s="25"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="131">
+      <c r="D64" s="126">
         <f t="array" ref="D64:E67">LINEST(K62:K67,L62:L67,TRUE,TRUE)</f>
-        <v>8.7203344167160974</v>
-      </c>
-      <c r="E64" s="132">
-        <v>200.56421713099689</v>
-      </c>
-      <c r="F64" s="26"/>
+        <v>8.7490599214527336</v>
+      </c>
+      <c r="E64" s="127">
+        <v>178.90781635930352</v>
+      </c>
       <c r="G64" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H64" s="21">
         <v>13</v>
@@ -11030,266 +9899,145 @@
       <c r="I64" s="21">
         <v>26.98</v>
       </c>
-      <c r="J64" s="39">
+      <c r="J64" s="38">
         <f t="shared" si="6"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K64" s="52">
-        <f t="shared" si="7"/>
-        <v>3716.6214715843644</v>
+      <c r="K64" s="51">
+        <f>(4300-69.99)*J64</f>
+        <v>3656.1269746550179</v>
       </c>
       <c r="L64" s="23">
         <v>397</v>
       </c>
-      <c r="M64" s="26"/>
-      <c r="N64" s="26"/>
-      <c r="O64" s="26"/>
-      <c r="P64" s="26"/>
-      <c r="Q64" s="26"/>
-      <c r="R64" s="26"/>
-      <c r="S64" s="85"/>
-      <c r="T64" s="26"/>
-      <c r="U64" s="26"/>
-      <c r="V64" s="26"/>
-      <c r="W64" s="82"/>
-      <c r="X64" s="26"/>
-      <c r="Y64" s="26"/>
-      <c r="Z64" s="26"/>
-      <c r="AA64" s="26"/>
-      <c r="AB64" s="26"/>
-      <c r="AC64" s="26"/>
-      <c r="AD64" s="26"/>
-      <c r="AE64" s="26"/>
-      <c r="AF64" s="26"/>
-      <c r="AG64" s="26"/>
-      <c r="AH64" s="129"/>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH64" s="124"/>
+    </row>
+    <row r="65" spans="2:34">
       <c r="B65" s="25"/>
-      <c r="C65" s="26"/>
       <c r="D65" s="25">
-        <v>0.27004832371656518</v>
-      </c>
-      <c r="E65" s="129">
-        <v>109.50069653454334</v>
-      </c>
-      <c r="F65" s="26"/>
-      <c r="G65" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="28">
+        <v>5.1158133798706262E-2</v>
+      </c>
+      <c r="E65" s="124">
+        <v>20.743884676896712</v>
+      </c>
+      <c r="G65" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="27">
         <v>14</v>
       </c>
-      <c r="I65" s="28">
+      <c r="I65" s="27">
         <v>28.09</v>
       </c>
-      <c r="J65" s="37">
+      <c r="J65" s="36">
         <f t="shared" si="6"/>
         <v>0.86932910407021868</v>
       </c>
-      <c r="K65" s="53">
+      <c r="K65" s="52">
         <f t="shared" si="7"/>
         <v>3738.1151475019406</v>
       </c>
-      <c r="L65" s="29">
+      <c r="L65" s="28">
         <v>406</v>
       </c>
-      <c r="M65" s="26"/>
-      <c r="N65" s="26"/>
-      <c r="O65" s="26"/>
-      <c r="P65" s="26"/>
-      <c r="Q65" s="26"/>
-      <c r="R65" s="26"/>
-      <c r="S65" s="85"/>
-      <c r="T65" s="26"/>
-      <c r="U65" s="26"/>
-      <c r="V65" s="26"/>
-      <c r="W65" s="82"/>
-      <c r="X65" s="26"/>
-      <c r="Y65" s="26"/>
-      <c r="Z65" s="26"/>
-      <c r="AA65" s="26"/>
-      <c r="AB65" s="26"/>
-      <c r="AC65" s="26"/>
-      <c r="AD65" s="26"/>
-      <c r="AE65" s="26"/>
-      <c r="AF65" s="26"/>
-      <c r="AG65" s="26"/>
-      <c r="AH65" s="129"/>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH65" s="124"/>
+    </row>
+    <row r="66" spans="2:34">
       <c r="B66" s="25"/>
-      <c r="C66" s="26"/>
       <c r="D66" s="25">
-        <v>0.99617867545651317</v>
-      </c>
-      <c r="E66" s="129">
-        <v>30.144226036304268</v>
-      </c>
-      <c r="F66" s="26"/>
-      <c r="G66" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H66" s="30">
+        <v>0.99986325633830953</v>
+      </c>
+      <c r="E66" s="124">
+        <v>5.7105422007442836</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="29">
         <v>50</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="29">
         <v>116</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="30">
         <f>((SQRT(1-(1/I66)^2*SIN(RADIANS(165))^2)+1/I66*COS(RADIANS(165)))/(1+1/I66))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K66" s="54">
+      <c r="K66" s="53">
         <f t="shared" si="7"/>
         <v>4156.6892178736107</v>
       </c>
-      <c r="L66" s="35">
+      <c r="L66" s="34">
         <v>454.5</v>
       </c>
-      <c r="M66" s="26"/>
-      <c r="N66" s="26"/>
-      <c r="O66" s="26"/>
-      <c r="P66" s="26"/>
-      <c r="Q66" s="26"/>
-      <c r="R66" s="26"/>
-      <c r="S66" s="85"/>
-      <c r="T66" s="26"/>
-      <c r="U66" s="26"/>
-      <c r="V66" s="26"/>
-      <c r="W66" s="82"/>
-      <c r="X66" s="26"/>
-      <c r="Y66" s="26"/>
-      <c r="Z66" s="26"/>
-      <c r="AA66" s="26"/>
-      <c r="AB66" s="26"/>
-      <c r="AC66" s="26"/>
-      <c r="AD66" s="26"/>
-      <c r="AE66" s="26"/>
-      <c r="AF66" s="26"/>
-      <c r="AG66" s="26"/>
-      <c r="AH66" s="129"/>
-    </row>
-    <row r="67" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH66" s="124"/>
+    </row>
+    <row r="67" spans="2:34" ht="15" thickBot="1">
       <c r="B67" s="25"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="61">
-        <v>1042.7574670718977</v>
-      </c>
-      <c r="E67" s="130">
+      <c r="D67" s="60">
+        <v>29247.812848588645</v>
+      </c>
+      <c r="E67" s="125">
         <v>4</v>
       </c>
-      <c r="F67" s="26"/>
-      <c r="G67" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H67" s="34">
+      <c r="G67" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="33">
         <v>78</v>
       </c>
-      <c r="I67" s="34">
+      <c r="I67" s="33">
         <v>195.1</v>
       </c>
-      <c r="J67" s="38">
+      <c r="J67" s="37">
         <f>((SQRT(1-(1/I67)^2*SIN(RADIANS(165))^2)+1/I67*COS(RADIANS(165)))/(1+1/I67))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K67" s="55">
+      <c r="K67" s="54">
         <f t="shared" si="7"/>
         <v>4214.208686636508</v>
       </c>
-      <c r="L67" s="36">
+      <c r="L67" s="35">
         <v>462</v>
       </c>
-      <c r="M67" s="26"/>
-      <c r="N67" s="26"/>
-      <c r="O67" s="26"/>
-      <c r="P67" s="26"/>
-      <c r="Q67" s="26"/>
-      <c r="R67" s="26"/>
-      <c r="S67" s="85"/>
-      <c r="T67" s="26"/>
-      <c r="U67" s="26"/>
-      <c r="V67" s="26"/>
-      <c r="W67" s="82"/>
-      <c r="X67" s="26"/>
-      <c r="Y67" s="26"/>
-      <c r="Z67" s="26"/>
-      <c r="AA67" s="26"/>
-      <c r="AB67" s="26"/>
-      <c r="AC67" s="26"/>
-      <c r="AD67" s="26"/>
-      <c r="AE67" s="26"/>
-      <c r="AF67" s="26"/>
-      <c r="AG67" s="26"/>
-      <c r="AH67" s="129"/>
-    </row>
-    <row r="68" spans="2:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH67" s="124"/>
+    </row>
+    <row r="68" spans="2:34" ht="44.1" thickBot="1">
       <c r="B68" s="25"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="26"/>
-      <c r="K68" s="26"/>
-      <c r="L68" s="26"/>
       <c r="M68" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R68" s="26"/>
-      <c r="S68" s="85"/>
-      <c r="T68" s="26"/>
-      <c r="U68" s="26"/>
-      <c r="V68" s="26"/>
-      <c r="W68" s="82"/>
-      <c r="X68" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z68" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB68" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD68" s="26"/>
-      <c r="AE68" s="26"/>
-      <c r="AF68" s="26"/>
-      <c r="AG68" s="26"/>
-      <c r="AH68" s="129"/>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH68" s="124"/>
+    </row>
+    <row r="69" spans="2:34">
       <c r="B69" s="25"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
-      <c r="L69" s="26"/>
       <c r="M69" s="4">
         <v>38.450000000000003</v>
       </c>
@@ -11308,625 +10056,386 @@
         <f>(($J$47/COS(RADIANS(0))*$N$69)+(1/COS(RADIANS(180-165))*$P$69))</f>
         <v>56.889220159669449</v>
       </c>
-      <c r="R69" s="26"/>
-      <c r="S69" s="85"/>
-      <c r="T69" s="26"/>
-      <c r="U69" s="26"/>
-      <c r="V69" s="26"/>
-      <c r="W69" s="82"/>
-      <c r="X69" s="26"/>
       <c r="Y69" s="17">
-        <v>65.209999999999994</v>
+        <v>64.39</v>
       </c>
       <c r="Z69" s="11">
         <f>Y69*$E$1/10</f>
-        <v>17.600178999999997</v>
+        <v>17.378861000000001</v>
       </c>
       <c r="AA69" s="17">
-        <v>70.73</v>
+        <v>71.59</v>
       </c>
       <c r="AB69" s="4">
         <f>AA69*$E$1/10</f>
-        <v>19.090026999999999</v>
+        <v>19.322140999999998</v>
       </c>
       <c r="AC69" s="10">
         <f>(($J$45/COS(RADIANS(0))*Z69)+(1/COS(RADIANS(180-165))*AB69))</f>
-        <v>34.975823067910518</v>
-      </c>
-      <c r="AD69" s="26"/>
-      <c r="AE69" s="26"/>
-      <c r="AF69" s="26"/>
-      <c r="AG69" s="26"/>
-      <c r="AH69" s="129"/>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.35">
+        <v>35.024833249099501</v>
+      </c>
+      <c r="AH69" s="124"/>
+    </row>
+    <row r="70" spans="2:34">
       <c r="B70" s="25"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="26"/>
-      <c r="O70" s="26"/>
-      <c r="P70" s="26"/>
-      <c r="Q70" s="26"/>
-      <c r="R70" s="26"/>
-      <c r="S70" s="85"/>
-      <c r="T70" s="26"/>
-      <c r="U70" s="26"/>
-      <c r="V70" s="26"/>
-      <c r="W70" s="82"/>
-      <c r="X70" s="26"/>
-      <c r="Y70" s="26"/>
-      <c r="Z70" s="26"/>
-      <c r="AA70" s="26"/>
-      <c r="AB70" s="26"/>
-      <c r="AC70" s="26"/>
-      <c r="AD70" s="26"/>
-      <c r="AE70" s="26"/>
-      <c r="AF70" s="26"/>
-      <c r="AG70" s="26"/>
-      <c r="AH70" s="129"/>
-    </row>
-    <row r="71" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH70" s="124"/>
+    </row>
+    <row r="71" spans="2:34" ht="15" thickBot="1">
       <c r="B71" s="25"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="26"/>
-      <c r="L71" s="26"/>
-      <c r="M71" s="26"/>
-      <c r="N71" s="26"/>
-      <c r="O71" s="26"/>
-      <c r="P71" s="26"/>
-      <c r="Q71" s="26"/>
-      <c r="R71" s="26"/>
-      <c r="S71" s="85"/>
-      <c r="T71" s="26"/>
-      <c r="U71" s="26"/>
-      <c r="V71" s="26"/>
-      <c r="W71" s="82"/>
-      <c r="X71" s="26"/>
-      <c r="Y71" s="26"/>
-      <c r="Z71" s="26"/>
-      <c r="AA71" s="26"/>
-      <c r="AB71" s="26"/>
-      <c r="AC71" s="26"/>
-      <c r="AD71" s="26"/>
-      <c r="AE71" s="26"/>
-      <c r="AF71" s="26"/>
-      <c r="AG71" s="26"/>
-      <c r="AH71" s="129"/>
-    </row>
-    <row r="72" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH71" s="124"/>
+    </row>
+    <row r="72" spans="2:34" ht="29.45" thickBot="1">
       <c r="B72" s="25"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
       <c r="M72" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N72" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O72" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P72" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q72" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="R72" s="69"/>
+      <c r="S72" s="82"/>
+      <c r="T72" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="U72" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="V72" s="93"/>
+      <c r="W72" s="94"/>
+      <c r="Z72" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N72" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O72" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P72" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72" s="104" t="s">
+      <c r="AA72" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC72" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD72" s="72"/>
+      <c r="AE72" s="72"/>
+      <c r="AF72" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="R72" s="70"/>
-      <c r="S72" s="86"/>
-      <c r="T72" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U72" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="V72" s="98"/>
-      <c r="W72" s="99"/>
-      <c r="X72" s="26"/>
-      <c r="Y72" s="26"/>
-      <c r="Z72" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA72" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB72" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD72" s="73"/>
-      <c r="AE72" s="73"/>
-      <c r="AF72" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG72" s="26"/>
-      <c r="AH72" s="129"/>
-    </row>
-    <row r="73" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH72" s="124"/>
+    </row>
+    <row r="73" spans="2:34" ht="15" thickBot="1">
       <c r="B73" s="25"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
       <c r="M73" s="18"/>
-      <c r="N73" s="65">
+      <c r="N73" s="64">
         <v>454.5</v>
       </c>
-      <c r="O73" s="66">
+      <c r="O73" s="65">
         <v>446.5</v>
       </c>
-      <c r="P73" s="103">
+      <c r="P73" s="98">
         <f>(N73-O73)*D64</f>
-        <v>69.762675333728779</v>
-      </c>
-      <c r="Q73" s="109">
+        <v>69.992479371621869</v>
+      </c>
+      <c r="Q73" s="104">
         <f>P73*10^3/Q69</f>
-        <v>1226.2898865185311</v>
-      </c>
-      <c r="R73" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S73" s="111">
+        <v>1230.3293870996272</v>
+      </c>
+      <c r="R73" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" s="106">
         <f>Q73/D64*D65</f>
-        <v>37.975324387801805</v>
-      </c>
-      <c r="T73" s="112">
+        <v>7.1940706735120781</v>
+      </c>
+      <c r="T73" s="107">
         <v>1349</v>
       </c>
-      <c r="U73" s="113">
+      <c r="U73" s="108">
         <v>1407</v>
       </c>
-      <c r="V73" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W73" s="115">
+      <c r="V73" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W73" s="110">
         <v>47</v>
       </c>
-      <c r="X73" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y73" s="26"/>
-      <c r="Z73" s="116">
+      <c r="X73" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z73" s="111">
         <v>397</v>
       </c>
       <c r="AA73" s="16">
         <v>392</v>
       </c>
-      <c r="AB73" s="71">
+      <c r="AB73" s="70">
         <f>(Z73-AA73)*D64</f>
-        <v>43.601672083580489</v>
-      </c>
-      <c r="AC73" s="117">
+        <v>43.745299607263668</v>
+      </c>
+      <c r="AC73" s="112">
         <f>AB73*10^3/AC69</f>
-        <v>1246.6231887930603</v>
-      </c>
-      <c r="AD73" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE73" s="122">
+        <v>1248.979525359721</v>
+      </c>
+      <c r="AD73" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE73" s="117">
         <f>AC73/D64*D65</f>
-        <v>38.604999114992673</v>
-      </c>
-      <c r="AF73" s="123">
+        <v>7.30312310623514</v>
+      </c>
+      <c r="AF73" s="118">
         <v>10.29</v>
       </c>
-      <c r="AG73" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH73" s="129"/>
-    </row>
-    <row r="74" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG73" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH73" s="124"/>
+    </row>
+    <row r="74" spans="2:34" ht="15" thickBot="1">
       <c r="B74" s="25"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
-      <c r="N74" s="26"/>
-      <c r="O74" s="26"/>
-      <c r="P74" s="26"/>
-      <c r="Q74" s="107"/>
-      <c r="R74" s="74"/>
-      <c r="S74" s="108"/>
-      <c r="T74" s="100"/>
-      <c r="U74" s="100"/>
-      <c r="V74" s="74"/>
-      <c r="W74" s="105"/>
-      <c r="X74" s="26"/>
-      <c r="Y74" s="26"/>
-      <c r="Z74" s="26"/>
-      <c r="AA74" s="26"/>
-      <c r="AB74" s="26"/>
-      <c r="AC74" s="69"/>
-      <c r="AD74" s="68"/>
-      <c r="AE74" s="87"/>
-      <c r="AF74" s="78"/>
-      <c r="AG74" s="26"/>
-      <c r="AH74" s="129"/>
-    </row>
-    <row r="75" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q74" s="102"/>
+      <c r="R74" s="73"/>
+      <c r="S74" s="103"/>
+      <c r="T74" s="95"/>
+      <c r="U74" s="95"/>
+      <c r="V74" s="73"/>
+      <c r="W74" s="100"/>
+      <c r="AC74" s="68"/>
+      <c r="AD74" s="67"/>
+      <c r="AE74" s="83"/>
+      <c r="AF74" s="76"/>
+      <c r="AH74" s="124"/>
+    </row>
+    <row r="75" spans="2:34" ht="15" thickBot="1">
       <c r="B75" s="25"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
-      <c r="N75" s="26"/>
-      <c r="O75" s="26"/>
-      <c r="P75" s="26"/>
-      <c r="Q75" s="94">
+      <c r="Q75" s="89">
         <f>Q73*$B$1*10^(-7)*10^3</f>
-        <v>0.89641790704504609</v>
-      </c>
-      <c r="R75" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S75" s="93">
+        <v>0.89937078196982745</v>
+      </c>
+      <c r="R75" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S75" s="88">
         <f>S73*$B$1*10^(-7)*10^3</f>
-        <v>2.7759962127483113E-2</v>
-      </c>
-      <c r="T75" s="79">
+        <v>5.2588656623373288E-3</v>
+      </c>
+      <c r="T75" s="131">
         <f>T73*$B$1*10^(-7)*10^3</f>
         <v>0.98611899999999997</v>
       </c>
-      <c r="U75" s="95">
+      <c r="U75" s="90">
         <f>U73*$B$1*10^(-7)*10^3</f>
         <v>1.0285170000000001</v>
       </c>
-      <c r="V75" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W75" s="106">
+      <c r="V75" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W75" s="101">
         <f>W73*$B$1*10^(-7)*10^3</f>
         <v>3.4356999999999999E-2</v>
       </c>
-      <c r="X75" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y75" s="26"/>
-      <c r="Z75" s="26"/>
-      <c r="AA75" s="26"/>
-      <c r="AB75" s="26"/>
-      <c r="AC75" s="118">
+      <c r="X75" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC75" s="113">
         <f>AC73*$E$1/10</f>
-        <v>336.46359865524698</v>
-      </c>
-      <c r="AD75" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE75" s="120">
+        <v>337.09957389458867</v>
+      </c>
+      <c r="AD75" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE75" s="115">
         <f>AE73*$E$1*10^(-7)*10^6</f>
-        <v>10.419489261136521</v>
-      </c>
-      <c r="AF75" s="124">
+        <v>1.9711129263728642</v>
+      </c>
+      <c r="AF75" s="119">
         <f>AF73*$E$1/10</f>
         <v>2.7772709999999998</v>
       </c>
-      <c r="AG75" s="67" t="s">
+      <c r="AG75" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH75" s="129"/>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH75" s="124"/>
+    </row>
+    <row r="76" spans="2:34">
       <c r="B76" s="25"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="26"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="26"/>
-      <c r="O76" s="26"/>
-      <c r="P76" s="26"/>
-      <c r="Q76" s="26"/>
-      <c r="R76" s="26"/>
-      <c r="S76" s="85"/>
-      <c r="T76" s="26"/>
-      <c r="U76" s="74"/>
-      <c r="V76" s="74"/>
-      <c r="W76" s="89"/>
-      <c r="X76" s="26"/>
-      <c r="Y76" s="26"/>
-      <c r="Z76" s="26"/>
-      <c r="AA76" s="26"/>
-      <c r="AB76" s="26"/>
-      <c r="AC76" s="26"/>
-      <c r="AD76" s="26"/>
-      <c r="AE76" s="26"/>
-      <c r="AF76" s="26"/>
-      <c r="AG76" s="26"/>
-      <c r="AH76" s="129"/>
-    </row>
-    <row r="77" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B77" s="61"/>
-      <c r="C77" s="62"/>
-      <c r="D77" s="62"/>
-      <c r="E77" s="62"/>
-      <c r="F77" s="62"/>
-      <c r="G77" s="62"/>
-      <c r="H77" s="62"/>
-      <c r="I77" s="62"/>
-      <c r="J77" s="62"/>
-      <c r="K77" s="62"/>
-      <c r="L77" s="62"/>
-      <c r="M77" s="62"/>
-      <c r="N77" s="62"/>
-      <c r="O77" s="62"/>
-      <c r="P77" s="62"/>
-      <c r="Q77" s="62"/>
-      <c r="R77" s="62"/>
-      <c r="S77" s="88"/>
-      <c r="T77" s="62"/>
-      <c r="U77" s="75"/>
-      <c r="V77" s="75"/>
-      <c r="W77" s="90"/>
-      <c r="X77" s="62"/>
-      <c r="Y77" s="62"/>
-      <c r="Z77" s="62"/>
-      <c r="AA77" s="62"/>
-      <c r="AB77" s="62"/>
-      <c r="AC77" s="62"/>
-      <c r="AD77" s="62"/>
-      <c r="AE77" s="62"/>
-      <c r="AF77" s="62"/>
-      <c r="AG77" s="62"/>
-      <c r="AH77" s="130"/>
-    </row>
-    <row r="78" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U78" s="77"/>
-      <c r="V78" s="77"/>
-      <c r="W78" s="91"/>
-      <c r="AD78" s="26"/>
-      <c r="AF78" s="26"/>
-    </row>
-    <row r="79" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B79" s="59"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="60"/>
-      <c r="K79" s="60"/>
-      <c r="L79" s="60"/>
-      <c r="M79" s="60"/>
-      <c r="N79" s="60"/>
-      <c r="O79" s="60"/>
-      <c r="P79" s="60"/>
-      <c r="Q79" s="60"/>
-      <c r="R79" s="60"/>
-      <c r="S79" s="84"/>
-      <c r="T79" s="60"/>
-      <c r="U79" s="60"/>
-      <c r="V79" s="60"/>
-      <c r="W79" s="81"/>
-      <c r="X79" s="60"/>
-      <c r="Y79" s="60"/>
-      <c r="Z79" s="60"/>
-      <c r="AA79" s="60"/>
-      <c r="AB79" s="60"/>
-      <c r="AC79" s="60"/>
-      <c r="AD79" s="60"/>
-      <c r="AE79" s="60"/>
-      <c r="AF79" s="60"/>
-      <c r="AG79" s="60"/>
-      <c r="AH79" s="128"/>
-    </row>
-    <row r="80" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U76" s="73"/>
+      <c r="V76" s="73"/>
+      <c r="W76" s="85"/>
+      <c r="AH76" s="124"/>
+    </row>
+    <row r="77" spans="2:34" ht="15" thickBot="1">
+      <c r="B77" s="60"/>
+      <c r="C77" s="61"/>
+      <c r="D77" s="61"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="61"/>
+      <c r="G77" s="61"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="61"/>
+      <c r="J77" s="61"/>
+      <c r="K77" s="61"/>
+      <c r="L77" s="61"/>
+      <c r="M77" s="61"/>
+      <c r="N77" s="61"/>
+      <c r="O77" s="61"/>
+      <c r="P77" s="61"/>
+      <c r="Q77" s="61"/>
+      <c r="R77" s="61"/>
+      <c r="S77" s="84"/>
+      <c r="T77" s="61"/>
+      <c r="U77" s="74"/>
+      <c r="V77" s="74"/>
+      <c r="W77" s="86"/>
+      <c r="X77" s="61"/>
+      <c r="Y77" s="61"/>
+      <c r="Z77" s="61"/>
+      <c r="AA77" s="61"/>
+      <c r="AB77" s="61"/>
+      <c r="AC77" s="61"/>
+      <c r="AD77" s="61"/>
+      <c r="AE77" s="61"/>
+      <c r="AF77" s="61"/>
+      <c r="AG77" s="61"/>
+      <c r="AH77" s="125"/>
+    </row>
+    <row r="78" spans="2:34" ht="15" thickBot="1">
+      <c r="U78" s="73"/>
+      <c r="V78" s="73"/>
+      <c r="W78" s="85"/>
+    </row>
+    <row r="79" spans="2:34" ht="15" thickBot="1">
+      <c r="B79" s="58"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
+      <c r="J79" s="59"/>
+      <c r="K79" s="59"/>
+      <c r="L79" s="59"/>
+      <c r="M79" s="59"/>
+      <c r="N79" s="59"/>
+      <c r="O79" s="59"/>
+      <c r="P79" s="59"/>
+      <c r="Q79" s="59"/>
+      <c r="R79" s="59"/>
+      <c r="S79" s="81"/>
+      <c r="T79" s="59"/>
+      <c r="U79" s="59"/>
+      <c r="V79" s="59"/>
+      <c r="W79" s="79"/>
+      <c r="X79" s="59"/>
+      <c r="Y79" s="59"/>
+      <c r="Z79" s="59"/>
+      <c r="AA79" s="59"/>
+      <c r="AB79" s="59"/>
+      <c r="AC79" s="59"/>
+      <c r="AD79" s="59"/>
+      <c r="AE79" s="59"/>
+      <c r="AF79" s="59"/>
+      <c r="AG79" s="59"/>
+      <c r="AH79" s="123"/>
+    </row>
+    <row r="80" spans="2:34" ht="29.45" thickBot="1">
       <c r="B80" s="25"/>
-      <c r="C80" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D80" s="57">
+      <c r="C80" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="56">
         <v>4.7</v>
       </c>
-      <c r="E80" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F80" s="26"/>
+      <c r="E80" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G80" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J80" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L80" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH80" s="124"/>
+    </row>
+    <row r="81" spans="2:34">
+      <c r="B81" s="25"/>
+      <c r="G81" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="45">
         <v>6</v>
       </c>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
-      <c r="R80" s="26"/>
-      <c r="S80" s="85"/>
-      <c r="T80" s="26"/>
-      <c r="U80" s="26"/>
-      <c r="V80" s="26"/>
-      <c r="W80" s="82"/>
-      <c r="X80" s="26"/>
-      <c r="Y80" s="26"/>
-      <c r="Z80" s="26"/>
-      <c r="AA80" s="26"/>
-      <c r="AB80" s="26"/>
-      <c r="AC80" s="26"/>
-      <c r="AD80" s="26"/>
-      <c r="AE80" s="26"/>
-      <c r="AF80" s="26"/>
-      <c r="AG80" s="26"/>
-      <c r="AH80" s="129"/>
-    </row>
-    <row r="81" spans="2:34" x14ac:dyDescent="0.35">
-      <c r="B81" s="25"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" s="46">
-        <v>6</v>
-      </c>
-      <c r="I81" s="46">
+      <c r="I81" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J81" s="47">
+      <c r="J81" s="46">
         <f>((SQRT(1-(1/I81)^2*SIN(RADIANS(165))^2)+1/I81*COS(RADIANS(165)))/(1+1/I81))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K81" s="50">
+      <c r="K81" s="49">
         <f>$D$80*1000*J81</f>
         <v>3385.2787056917609</v>
       </c>
-      <c r="L81" s="48">
+      <c r="L81" s="47">
         <v>317.5</v>
       </c>
-      <c r="M81" s="26"/>
-      <c r="N81" s="26"/>
-      <c r="O81" s="26"/>
-      <c r="P81" s="26"/>
-      <c r="Q81" s="26"/>
-      <c r="R81" s="26"/>
-      <c r="S81" s="85"/>
-      <c r="T81" s="26"/>
-      <c r="U81" s="26"/>
-      <c r="V81" s="26"/>
-      <c r="W81" s="82"/>
-      <c r="X81" s="26"/>
-      <c r="Y81" s="26"/>
-      <c r="Z81" s="26"/>
-      <c r="AA81" s="26"/>
-      <c r="AB81" s="26"/>
-      <c r="AC81" s="26"/>
-      <c r="AD81" s="26"/>
-      <c r="AE81" s="26"/>
-      <c r="AF81" s="26"/>
-      <c r="AG81" s="26"/>
-      <c r="AH81" s="129"/>
-    </row>
-    <row r="82" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH81" s="124"/>
+    </row>
+    <row r="82" spans="2:34" ht="15" thickBot="1">
       <c r="B82" s="25"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H82" s="41">
+      <c r="G82" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="40">
         <v>8</v>
       </c>
-      <c r="I82" s="42">
+      <c r="I82" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J82" s="43">
+      <c r="J82" s="42">
         <f t="shared" ref="J82:J83" si="8">((SQRT(1-(1/I82)^2*SIN(RADIANS(165))^2)+1/I82*COS(RADIANS(165)))/(1+1/I82))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K82" s="51">
+      <c r="K82" s="50">
         <f t="shared" ref="K82:K83" si="9">$D$80*1000*J82</f>
         <v>3674.7325474532204</v>
       </c>
-      <c r="L82" s="44">
+      <c r="L82" s="43">
         <v>346.5</v>
       </c>
-      <c r="M82" s="26"/>
-      <c r="N82" s="26"/>
-      <c r="O82" s="26"/>
-      <c r="P82" s="26"/>
-      <c r="Q82" s="26"/>
-      <c r="R82" s="26"/>
-      <c r="S82" s="85"/>
-      <c r="T82" s="26"/>
-      <c r="U82" s="26"/>
-      <c r="V82" s="26"/>
-      <c r="W82" s="82"/>
-      <c r="X82" s="26"/>
-      <c r="Y82" s="26"/>
-      <c r="Z82" s="26"/>
-      <c r="AA82" s="26"/>
-      <c r="AB82" s="26"/>
-      <c r="AC82" s="26"/>
-      <c r="AD82" s="26"/>
-      <c r="AE82" s="26"/>
-      <c r="AF82" s="26"/>
-      <c r="AG82" s="26"/>
-      <c r="AH82" s="129"/>
-    </row>
-    <row r="83" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH82" s="124"/>
+    </row>
+    <row r="83" spans="2:34" ht="15" thickBot="1">
       <c r="B83" s="25"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="131">
+      <c r="D83" s="126">
         <f t="array" ref="D83:E86">LINEST(K81:K84,L81:L84,TRUE,TRUE)</f>
-        <v>10.028282738820089</v>
-      </c>
-      <c r="E83" s="132">
-        <v>215.99440361817187</v>
-      </c>
-      <c r="F83" s="26"/>
+        <v>9.9402332227943919</v>
+      </c>
+      <c r="E83" s="127">
+        <v>230.22785246571448</v>
+      </c>
       <c r="G83" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H83" s="21">
         <v>13</v>
@@ -11934,250 +10443,129 @@
       <c r="I83" s="21">
         <v>26.98</v>
       </c>
-      <c r="J83" s="39">
+      <c r="J83" s="38">
         <f t="shared" si="8"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K83" s="52">
-        <f t="shared" si="9"/>
-        <v>4062.3537014991889</v>
+      <c r="K83" s="51">
+        <f>(4700-84.49)*J83</f>
+        <v>3989.32641123543</v>
       </c>
       <c r="L83" s="23">
         <v>378</v>
       </c>
-      <c r="M83" s="26"/>
-      <c r="N83" s="26"/>
-      <c r="O83" s="26"/>
-      <c r="P83" s="26"/>
-      <c r="Q83" s="26"/>
-      <c r="R83" s="26"/>
-      <c r="S83" s="85"/>
-      <c r="T83" s="26"/>
-      <c r="U83" s="26"/>
-      <c r="V83" s="26"/>
-      <c r="W83" s="82"/>
-      <c r="X83" s="26"/>
-      <c r="Y83" s="26"/>
-      <c r="Z83" s="26"/>
-      <c r="AA83" s="26"/>
-      <c r="AB83" s="26"/>
-      <c r="AC83" s="26"/>
-      <c r="AD83" s="26"/>
-      <c r="AE83" s="26"/>
-      <c r="AF83" s="26"/>
-      <c r="AG83" s="26"/>
-      <c r="AH83" s="129"/>
-    </row>
-    <row r="84" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH83" s="124"/>
+    </row>
+    <row r="84" spans="2:34">
       <c r="B84" s="25"/>
-      <c r="C84" s="26"/>
       <c r="D84" s="25">
-        <v>0.52999498018827829</v>
-      </c>
-      <c r="E84" s="129">
-        <v>196.90374545342524</v>
-      </c>
-      <c r="F84" s="26"/>
-      <c r="G84" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="28">
+        <v>1.7775769031469803E-2</v>
+      </c>
+      <c r="E84" s="124">
+        <v>6.6040540598479067</v>
+      </c>
+      <c r="G84" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="27">
         <v>50</v>
       </c>
-      <c r="I84" s="28">
+      <c r="I84" s="27">
         <v>116</v>
       </c>
-      <c r="J84" s="37">
+      <c r="J84" s="36">
         <f>((SQRT(1-(1/I84)^2*SIN(RADIANS(165))^2)+1/I84*COS(RADIANS(165)))/(1+1/I84))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K84" s="53">
+      <c r="K84" s="52">
         <f>$D$80*1000*J84</f>
         <v>4543.3579823269692</v>
       </c>
-      <c r="L84" s="29">
+      <c r="L84" s="28">
         <v>434</v>
       </c>
-      <c r="M84" s="26"/>
-      <c r="N84" s="26"/>
-      <c r="O84" s="26"/>
-      <c r="P84" s="26"/>
-      <c r="Q84" s="26"/>
-      <c r="R84" s="26"/>
-      <c r="S84" s="85"/>
-      <c r="T84" s="26"/>
-      <c r="U84" s="26"/>
-      <c r="V84" s="26"/>
-      <c r="W84" s="82"/>
-      <c r="X84" s="26"/>
-      <c r="Y84" s="26"/>
-      <c r="Z84" s="26"/>
-      <c r="AA84" s="26"/>
-      <c r="AB84" s="26"/>
-      <c r="AC84" s="26"/>
-      <c r="AD84" s="26"/>
-      <c r="AE84" s="26"/>
-      <c r="AF84" s="26"/>
-      <c r="AG84" s="26"/>
-      <c r="AH84" s="129"/>
-    </row>
-    <row r="85" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH84" s="124"/>
+    </row>
+    <row r="85" spans="2:34">
       <c r="B85" s="25"/>
-      <c r="C85" s="26"/>
       <c r="D85" s="25">
-        <v>0.99444478282660387</v>
-      </c>
-      <c r="E85" s="129">
-        <v>45.790155400265043</v>
-      </c>
-      <c r="F85" s="26"/>
-      <c r="G85" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="H85" s="30">
+        <v>0.99999360425901995</v>
+      </c>
+      <c r="E85" s="124">
+        <v>1.5357791238344698</v>
+      </c>
+      <c r="G85" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" s="29">
         <v>78</v>
       </c>
-      <c r="I85" s="30">
+      <c r="I85" s="29">
         <v>195.1</v>
       </c>
-      <c r="J85" s="31">
+      <c r="J85" s="30">
         <f>((SQRT(1-(1/I85)^2*SIN(RADIANS(165))^2)+1/I85*COS(RADIANS(165)))/(1+1/I85))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K85" s="54">
+      <c r="K85" s="53">
         <f>$D$80*1000*J85</f>
         <v>4606.2280993468812</v>
       </c>
-      <c r="L85" s="35"/>
-      <c r="M85" s="26"/>
-      <c r="N85" s="26"/>
-      <c r="O85" s="26"/>
-      <c r="P85" s="26"/>
-      <c r="Q85" s="26"/>
-      <c r="R85" s="26"/>
-      <c r="S85" s="85"/>
-      <c r="T85" s="26"/>
-      <c r="U85" s="26"/>
-      <c r="V85" s="26"/>
-      <c r="W85" s="82"/>
-      <c r="X85" s="26"/>
-      <c r="Y85" s="26"/>
-      <c r="Z85" s="26"/>
-      <c r="AA85" s="26"/>
-      <c r="AB85" s="26"/>
-      <c r="AC85" s="26"/>
-      <c r="AD85" s="26"/>
-      <c r="AE85" s="26"/>
-      <c r="AF85" s="26"/>
-      <c r="AG85" s="26"/>
-      <c r="AH85" s="129"/>
-    </row>
-    <row r="86" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L85" s="34"/>
+      <c r="AH85" s="124"/>
+    </row>
+    <row r="86" spans="2:34" ht="15" thickBot="1">
       <c r="B86" s="25"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="61">
-        <v>358.02192849956941</v>
-      </c>
-      <c r="E86" s="130">
+      <c r="D86" s="60">
+        <v>312706.09844523517</v>
+      </c>
+      <c r="E86" s="125">
         <v>2</v>
       </c>
-      <c r="F86" s="26"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="34"/>
-      <c r="I86" s="34"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="55"/>
-      <c r="L86" s="36"/>
-      <c r="M86" s="26"/>
-      <c r="N86" s="26"/>
-      <c r="O86" s="26"/>
-      <c r="P86" s="26"/>
-      <c r="Q86" s="26"/>
-      <c r="R86" s="26"/>
-      <c r="S86" s="85"/>
-      <c r="T86" s="26"/>
-      <c r="U86" s="26"/>
-      <c r="V86" s="26"/>
-      <c r="W86" s="82"/>
-      <c r="X86" s="26"/>
-      <c r="Y86" s="26"/>
-      <c r="Z86" s="26"/>
-      <c r="AA86" s="26"/>
-      <c r="AB86" s="26"/>
-      <c r="AC86" s="26"/>
-      <c r="AD86" s="26"/>
-      <c r="AE86" s="26"/>
-      <c r="AF86" s="26"/>
-      <c r="AG86" s="26"/>
-      <c r="AH86" s="129"/>
-    </row>
-    <row r="87" spans="2:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G86" s="32"/>
+      <c r="H86" s="33"/>
+      <c r="I86" s="33"/>
+      <c r="J86" s="37"/>
+      <c r="K86" s="54"/>
+      <c r="L86" s="35"/>
+      <c r="AH86" s="124"/>
+    </row>
+    <row r="87" spans="2:34" ht="44.1" thickBot="1">
       <c r="B87" s="25"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="26"/>
-      <c r="I87" s="26"/>
-      <c r="J87" s="26"/>
-      <c r="K87" s="26"/>
-      <c r="L87" s="26"/>
       <c r="M87" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R87" s="26"/>
-      <c r="S87" s="85"/>
-      <c r="T87" s="26"/>
-      <c r="U87" s="26"/>
-      <c r="V87" s="26"/>
-      <c r="W87" s="82"/>
-      <c r="X87" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z87" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA87" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB87" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD87" s="26"/>
-      <c r="AE87" s="26"/>
-      <c r="AF87" s="26"/>
-      <c r="AG87" s="26"/>
-      <c r="AH87" s="129"/>
-    </row>
-    <row r="88" spans="2:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH87" s="124"/>
+    </row>
+    <row r="88" spans="2:34">
       <c r="B88" s="25"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="26"/>
-      <c r="H88" s="26"/>
-      <c r="I88" s="26"/>
-      <c r="J88" s="26"/>
-      <c r="K88" s="26"/>
-      <c r="L88" s="26"/>
       <c r="M88" s="4">
         <v>36.340000000000003</v>
       </c>
@@ -12196,625 +10584,386 @@
         <f>(($J$47/COS(RADIANS(0))*$N$88)+(1/COS(RADIANS(180-165))*$P$88))</f>
         <v>53.778691797155474</v>
       </c>
-      <c r="R88" s="26"/>
-      <c r="S88" s="85"/>
-      <c r="T88" s="26"/>
-      <c r="U88" s="26"/>
-      <c r="V88" s="26"/>
-      <c r="W88" s="82"/>
-      <c r="X88" s="26"/>
       <c r="Y88" s="17">
-        <v>61.11</v>
+        <v>60.41</v>
       </c>
       <c r="Z88" s="11">
         <f>Y88*$E$1/10</f>
-        <v>16.493589</v>
+        <v>16.304658999999997</v>
       </c>
       <c r="AA88" s="17">
-        <v>66.319999999999993</v>
+        <v>67.2</v>
       </c>
       <c r="AB88" s="4">
         <f>AA88*$E$1/10</f>
-        <v>17.899767999999998</v>
+        <v>18.137279999999997</v>
       </c>
       <c r="AC88" s="10">
         <f>(($J$45/COS(RADIANS(0))*Z88)+(1/COS(RADIANS(180-165))*AB88))</f>
-        <v>32.787116705938182</v>
-      </c>
-      <c r="AD88" s="26"/>
-      <c r="AE88" s="26"/>
-      <c r="AF88" s="26"/>
-      <c r="AG88" s="26"/>
-      <c r="AH88" s="129"/>
-    </row>
-    <row r="89" spans="2:34" x14ac:dyDescent="0.35">
+        <v>32.869709246605218</v>
+      </c>
+      <c r="AH88" s="124"/>
+    </row>
+    <row r="89" spans="2:34">
       <c r="B89" s="25"/>
-      <c r="C89" s="26"/>
-      <c r="D89" s="26"/>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="26"/>
-      <c r="H89" s="26"/>
-      <c r="I89" s="26"/>
-      <c r="J89" s="26"/>
-      <c r="K89" s="26"/>
-      <c r="L89" s="26"/>
-      <c r="M89" s="26"/>
-      <c r="N89" s="26"/>
-      <c r="O89" s="26"/>
-      <c r="P89" s="26"/>
-      <c r="Q89" s="26"/>
-      <c r="R89" s="26"/>
-      <c r="S89" s="85"/>
-      <c r="T89" s="26"/>
-      <c r="U89" s="26"/>
-      <c r="V89" s="26"/>
-      <c r="W89" s="82"/>
-      <c r="X89" s="26"/>
-      <c r="Y89" s="26"/>
-      <c r="Z89" s="26"/>
-      <c r="AA89" s="26"/>
-      <c r="AB89" s="26"/>
-      <c r="AC89" s="26"/>
-      <c r="AD89" s="26"/>
-      <c r="AE89" s="26"/>
-      <c r="AF89" s="26"/>
-      <c r="AG89" s="26"/>
-      <c r="AH89" s="129"/>
-    </row>
-    <row r="90" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH89" s="124"/>
+    </row>
+    <row r="90" spans="2:34" ht="15" thickBot="1">
       <c r="B90" s="25"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="26"/>
-      <c r="K90" s="26"/>
-      <c r="L90" s="26"/>
-      <c r="M90" s="26"/>
-      <c r="N90" s="26"/>
-      <c r="O90" s="26"/>
-      <c r="P90" s="26"/>
-      <c r="Q90" s="26"/>
-      <c r="R90" s="26"/>
-      <c r="S90" s="85"/>
-      <c r="T90" s="26"/>
-      <c r="U90" s="26"/>
-      <c r="V90" s="26"/>
-      <c r="W90" s="82"/>
-      <c r="X90" s="26"/>
-      <c r="Y90" s="26"/>
-      <c r="Z90" s="26"/>
-      <c r="AA90" s="26"/>
-      <c r="AB90" s="26"/>
-      <c r="AC90" s="26"/>
-      <c r="AD90" s="26"/>
-      <c r="AE90" s="26"/>
-      <c r="AF90" s="26"/>
-      <c r="AG90" s="26"/>
-      <c r="AH90" s="129"/>
-    </row>
-    <row r="91" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH90" s="124"/>
+    </row>
+    <row r="91" spans="2:34" ht="29.45" thickBot="1">
       <c r="B91" s="25"/>
-      <c r="C91" s="26"/>
-      <c r="D91" s="26"/>
-      <c r="E91" s="26"/>
-      <c r="F91" s="26"/>
-      <c r="G91" s="26"/>
-      <c r="H91" s="26"/>
-      <c r="I91" s="26"/>
-      <c r="J91" s="26"/>
-      <c r="K91" s="26"/>
-      <c r="L91" s="26"/>
       <c r="M91" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N91" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O91" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P91" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q91" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="R91" s="69"/>
+      <c r="S91" s="82"/>
+      <c r="T91" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="U91" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="V91" s="93"/>
+      <c r="W91" s="94"/>
+      <c r="Z91" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA91" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="N91" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O91" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P91" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="104" t="s">
+      <c r="AB91" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC91" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD91" s="72"/>
+      <c r="AE91" s="72"/>
+      <c r="AF91" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="R91" s="70"/>
-      <c r="S91" s="86"/>
-      <c r="T91" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U91" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="V91" s="98"/>
-      <c r="W91" s="99"/>
-      <c r="X91" s="26"/>
-      <c r="Y91" s="26"/>
-      <c r="Z91" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB91" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC91" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD91" s="73"/>
-      <c r="AE91" s="73"/>
-      <c r="AF91" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG91" s="26"/>
-      <c r="AH91" s="129"/>
-    </row>
-    <row r="92" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH91" s="124"/>
+    </row>
+    <row r="92" spans="2:34" ht="15" thickBot="1">
       <c r="B92" s="25"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="26"/>
-      <c r="J92" s="26"/>
-      <c r="K92" s="26"/>
-      <c r="L92" s="26"/>
       <c r="M92" s="18"/>
-      <c r="N92" s="65">
+      <c r="N92" s="64">
         <v>434</v>
       </c>
-      <c r="O92" s="66">
+      <c r="O92" s="65">
         <v>425.5</v>
       </c>
-      <c r="P92" s="103">
+      <c r="P92" s="98">
         <f>(N92-O92)*D83</f>
-        <v>85.240403279970749</v>
-      </c>
-      <c r="Q92" s="109">
+        <v>84.491982393752338</v>
+      </c>
+      <c r="Q92" s="104">
         <f>P92*10^3/Q88</f>
-        <v>1585.021881928325</v>
-      </c>
-      <c r="R92" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S92" s="111">
+        <v>1571.1052011536915</v>
+      </c>
+      <c r="R92" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S92" s="106">
         <f>Q92/D83*D84</f>
-        <v>83.768443988789002</v>
-      </c>
-      <c r="T92" s="112">
+        <v>2.8095521054583399</v>
+      </c>
+      <c r="T92" s="107">
         <v>1497</v>
       </c>
-      <c r="U92" s="113">
+      <c r="U92" s="108">
         <v>1661</v>
       </c>
-      <c r="V92" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W92" s="115">
+      <c r="V92" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W92" s="110">
         <v>66</v>
       </c>
-      <c r="X92" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y92" s="26"/>
-      <c r="Z92" s="116">
+      <c r="X92" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z92" s="111">
         <v>378</v>
       </c>
       <c r="AA92" s="16">
         <v>373.5</v>
       </c>
-      <c r="AB92" s="71">
+      <c r="AB92" s="70">
         <f>(Z92-AA92)*D83</f>
-        <v>45.127272324690395</v>
-      </c>
-      <c r="AC92" s="117">
+        <v>44.731049502574763</v>
+      </c>
+      <c r="AC92" s="112">
         <f>AB92*10^3/AC88</f>
-        <v>1376.3720893614668</v>
-      </c>
-      <c r="AD92" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE92" s="122">
+        <v>1360.8592995751731</v>
+      </c>
+      <c r="AD92" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE92" s="117">
         <f>AC92/D83*D84</f>
-        <v>72.741297511388083</v>
-      </c>
-      <c r="AF92" s="123">
+        <v>2.433576763380576</v>
+      </c>
+      <c r="AF92" s="118">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AG92" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH92" s="129"/>
-    </row>
-    <row r="93" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG92" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH92" s="124"/>
+    </row>
+    <row r="93" spans="2:34" ht="15" thickBot="1">
       <c r="B93" s="25"/>
-      <c r="C93" s="26"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
-      <c r="H93" s="26"/>
-      <c r="I93" s="26"/>
-      <c r="J93" s="26"/>
-      <c r="K93" s="26"/>
-      <c r="L93" s="26"/>
-      <c r="M93" s="26"/>
-      <c r="N93" s="26"/>
-      <c r="O93" s="26"/>
-      <c r="P93" s="26"/>
-      <c r="Q93" s="107"/>
-      <c r="R93" s="74"/>
-      <c r="S93" s="108"/>
-      <c r="T93" s="100"/>
-      <c r="U93" s="100"/>
-      <c r="V93" s="74"/>
-      <c r="W93" s="105"/>
-      <c r="X93" s="26"/>
-      <c r="Y93" s="26"/>
-      <c r="Z93" s="26"/>
-      <c r="AA93" s="26"/>
-      <c r="AB93" s="26"/>
-      <c r="AC93" s="69"/>
-      <c r="AD93" s="68"/>
-      <c r="AE93" s="87"/>
-      <c r="AF93" s="78"/>
-      <c r="AG93" s="26"/>
-      <c r="AH93" s="129"/>
-    </row>
-    <row r="94" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q93" s="102"/>
+      <c r="R93" s="73"/>
+      <c r="S93" s="103"/>
+      <c r="T93" s="95"/>
+      <c r="U93" s="95"/>
+      <c r="V93" s="73"/>
+      <c r="W93" s="100"/>
+      <c r="AC93" s="68"/>
+      <c r="AD93" s="67"/>
+      <c r="AE93" s="83"/>
+      <c r="AF93" s="76"/>
+      <c r="AH93" s="124"/>
+    </row>
+    <row r="94" spans="2:34" ht="15" thickBot="1">
       <c r="B94" s="25"/>
-      <c r="C94" s="26"/>
-      <c r="D94" s="26"/>
-      <c r="E94" s="26"/>
-      <c r="F94" s="26"/>
-      <c r="G94" s="26"/>
-      <c r="H94" s="26"/>
-      <c r="I94" s="26"/>
-      <c r="J94" s="26"/>
-      <c r="K94" s="26"/>
-      <c r="L94" s="26"/>
-      <c r="M94" s="26"/>
-      <c r="N94" s="26"/>
-      <c r="O94" s="26"/>
-      <c r="P94" s="26"/>
-      <c r="Q94" s="94">
+      <c r="Q94" s="89">
         <f>Q92*$B$1*10^(-7)*10^3</f>
-        <v>1.1586509956896056</v>
-      </c>
-      <c r="R94" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S94" s="93">
+        <v>1.1484779020433484</v>
+      </c>
+      <c r="R94" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S94" s="88">
         <f>S92*$B$1*10^(-7)*10^3</f>
-        <v>6.1234732555804756E-2</v>
-      </c>
-      <c r="T94" s="79">
+        <v>2.0537825890900464E-3</v>
+      </c>
+      <c r="T94" s="131">
         <f>T92*$B$1*10^(-7)*10^3</f>
         <v>1.0943069999999999</v>
       </c>
-      <c r="U94" s="95">
+      <c r="U94" s="90">
         <f>U92*$B$1*10^(-7)*10^3</f>
         <v>1.2141909999999998</v>
       </c>
-      <c r="V94" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W94" s="106">
+      <c r="V94" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W94" s="101">
         <f>W92*$B$1*10^(-7)*10^3</f>
         <v>4.8245999999999997E-2</v>
       </c>
-      <c r="X94" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y94" s="26"/>
-      <c r="Z94" s="26"/>
-      <c r="AA94" s="26"/>
-      <c r="AB94" s="26"/>
-      <c r="AC94" s="118">
+      <c r="X94" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC94" s="113">
         <f>AC92*$E$1/10</f>
-        <v>371.4828269186599</v>
-      </c>
-      <c r="AD94" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE94" s="120">
+        <v>367.29592495533922</v>
+      </c>
+      <c r="AD94" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE94" s="115">
         <f>AE92*$E$1*10^(-7)*10^6</f>
-        <v>19.63287619832364</v>
-      </c>
-      <c r="AF94" s="124">
+        <v>0.6568223684364175</v>
+      </c>
+      <c r="AF94" s="119">
         <f>AF92*$E$1/10</f>
         <v>2.5100699999999998</v>
       </c>
-      <c r="AG94" s="67" t="s">
+      <c r="AG94" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH94" s="129"/>
-    </row>
-    <row r="95" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH94" s="124"/>
+    </row>
+    <row r="95" spans="2:34">
       <c r="B95" s="25"/>
-      <c r="C95" s="26"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26"/>
-      <c r="H95" s="26"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="26"/>
-      <c r="K95" s="26"/>
-      <c r="L95" s="26"/>
-      <c r="M95" s="26"/>
-      <c r="N95" s="26"/>
-      <c r="O95" s="26"/>
-      <c r="P95" s="26"/>
-      <c r="Q95" s="26"/>
-      <c r="R95" s="26"/>
-      <c r="S95" s="85"/>
-      <c r="T95" s="26"/>
-      <c r="U95" s="74"/>
-      <c r="V95" s="74"/>
-      <c r="W95" s="89"/>
-      <c r="X95" s="26"/>
-      <c r="Y95" s="26"/>
-      <c r="Z95" s="26"/>
-      <c r="AA95" s="26"/>
-      <c r="AB95" s="26"/>
-      <c r="AC95" s="26"/>
-      <c r="AD95" s="26"/>
-      <c r="AE95" s="26"/>
-      <c r="AF95" s="26"/>
-      <c r="AG95" s="26"/>
-      <c r="AH95" s="129"/>
-    </row>
-    <row r="96" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="61"/>
-      <c r="C96" s="62"/>
-      <c r="D96" s="62"/>
-      <c r="E96" s="62"/>
-      <c r="F96" s="62"/>
-      <c r="G96" s="62"/>
-      <c r="H96" s="62"/>
-      <c r="I96" s="62"/>
-      <c r="J96" s="62"/>
-      <c r="K96" s="62"/>
-      <c r="L96" s="62"/>
-      <c r="M96" s="62"/>
-      <c r="N96" s="62"/>
-      <c r="O96" s="62"/>
-      <c r="P96" s="62"/>
-      <c r="Q96" s="62"/>
-      <c r="R96" s="62"/>
-      <c r="S96" s="88"/>
-      <c r="T96" s="62"/>
-      <c r="U96" s="75"/>
-      <c r="V96" s="75"/>
-      <c r="W96" s="90"/>
-      <c r="X96" s="62"/>
-      <c r="Y96" s="62"/>
-      <c r="Z96" s="62"/>
-      <c r="AA96" s="62"/>
-      <c r="AB96" s="62"/>
-      <c r="AC96" s="62"/>
-      <c r="AD96" s="62"/>
-      <c r="AE96" s="62"/>
-      <c r="AF96" s="62"/>
-      <c r="AG96" s="62"/>
-      <c r="AH96" s="130"/>
-    </row>
-    <row r="97" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U97" s="77"/>
-      <c r="V97" s="77"/>
-      <c r="W97" s="91"/>
-      <c r="AD97" s="26"/>
-      <c r="AF97" s="26"/>
-    </row>
-    <row r="98" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="59"/>
-      <c r="C98" s="60"/>
-      <c r="D98" s="60"/>
-      <c r="E98" s="60"/>
-      <c r="F98" s="60"/>
-      <c r="G98" s="60"/>
-      <c r="H98" s="60"/>
-      <c r="I98" s="60"/>
-      <c r="J98" s="60"/>
-      <c r="K98" s="60"/>
-      <c r="L98" s="60"/>
-      <c r="M98" s="60"/>
-      <c r="N98" s="60"/>
-      <c r="O98" s="60"/>
-      <c r="P98" s="60"/>
-      <c r="Q98" s="60"/>
-      <c r="R98" s="60"/>
-      <c r="S98" s="84"/>
-      <c r="T98" s="60"/>
-      <c r="U98" s="60"/>
-      <c r="V98" s="60"/>
-      <c r="W98" s="81"/>
-      <c r="X98" s="60"/>
-      <c r="Y98" s="60"/>
-      <c r="Z98" s="60"/>
-      <c r="AA98" s="60"/>
-      <c r="AB98" s="60"/>
-      <c r="AC98" s="60"/>
-      <c r="AD98" s="60"/>
-      <c r="AE98" s="60"/>
-      <c r="AF98" s="60"/>
-      <c r="AG98" s="60"/>
-      <c r="AH98" s="128"/>
-    </row>
-    <row r="99" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U95" s="73"/>
+      <c r="V95" s="73"/>
+      <c r="W95" s="85"/>
+      <c r="AH95" s="124"/>
+    </row>
+    <row r="96" spans="2:34" ht="15" thickBot="1">
+      <c r="B96" s="60"/>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="61"/>
+      <c r="I96" s="61"/>
+      <c r="J96" s="61"/>
+      <c r="K96" s="61"/>
+      <c r="L96" s="61"/>
+      <c r="M96" s="61"/>
+      <c r="N96" s="61"/>
+      <c r="O96" s="61"/>
+      <c r="P96" s="61"/>
+      <c r="Q96" s="61"/>
+      <c r="R96" s="61"/>
+      <c r="S96" s="84"/>
+      <c r="T96" s="61"/>
+      <c r="U96" s="74"/>
+      <c r="V96" s="74"/>
+      <c r="W96" s="86"/>
+      <c r="X96" s="61"/>
+      <c r="Y96" s="61"/>
+      <c r="Z96" s="61"/>
+      <c r="AA96" s="61"/>
+      <c r="AB96" s="61"/>
+      <c r="AC96" s="61"/>
+      <c r="AD96" s="61"/>
+      <c r="AE96" s="61"/>
+      <c r="AF96" s="61"/>
+      <c r="AG96" s="61"/>
+      <c r="AH96" s="125"/>
+    </row>
+    <row r="97" spans="2:34" ht="15" thickBot="1">
+      <c r="U97" s="73"/>
+      <c r="V97" s="73"/>
+      <c r="W97" s="85"/>
+    </row>
+    <row r="98" spans="2:34" ht="15" thickBot="1">
+      <c r="B98" s="58"/>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="59"/>
+      <c r="H98" s="59"/>
+      <c r="I98" s="59"/>
+      <c r="J98" s="59"/>
+      <c r="K98" s="59"/>
+      <c r="L98" s="59"/>
+      <c r="M98" s="59"/>
+      <c r="N98" s="59"/>
+      <c r="O98" s="59"/>
+      <c r="P98" s="59"/>
+      <c r="Q98" s="59"/>
+      <c r="R98" s="59"/>
+      <c r="S98" s="81"/>
+      <c r="T98" s="59"/>
+      <c r="U98" s="59"/>
+      <c r="V98" s="59"/>
+      <c r="W98" s="79"/>
+      <c r="X98" s="59"/>
+      <c r="Y98" s="59"/>
+      <c r="Z98" s="59"/>
+      <c r="AA98" s="59"/>
+      <c r="AB98" s="59"/>
+      <c r="AC98" s="59"/>
+      <c r="AD98" s="59"/>
+      <c r="AE98" s="59"/>
+      <c r="AF98" s="59"/>
+      <c r="AG98" s="59"/>
+      <c r="AH98" s="123"/>
+    </row>
+    <row r="99" spans="2:34" ht="29.45" thickBot="1">
       <c r="B99" s="25"/>
-      <c r="C99" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D99" s="57">
+      <c r="C99" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="E99" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F99" s="26"/>
+      <c r="D99" s="56">
+        <v>5</v>
+      </c>
+      <c r="E99" s="57" t="s">
+        <v>6</v>
+      </c>
       <c r="G99" s="24" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I99" s="19" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J99" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K99" s="19" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L99" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH99" s="124"/>
+    </row>
+    <row r="100" spans="2:34">
+      <c r="B100" s="25"/>
+      <c r="G100" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" s="45">
         <v>6</v>
       </c>
-      <c r="M99" s="26"/>
-      <c r="N99" s="26"/>
-      <c r="O99" s="26"/>
-      <c r="P99" s="26"/>
-      <c r="Q99" s="26"/>
-      <c r="R99" s="26"/>
-      <c r="S99" s="85"/>
-      <c r="T99" s="26"/>
-      <c r="U99" s="26"/>
-      <c r="V99" s="26"/>
-      <c r="W99" s="82"/>
-      <c r="X99" s="26"/>
-      <c r="Y99" s="26"/>
-      <c r="Z99" s="26"/>
-      <c r="AA99" s="26"/>
-      <c r="AB99" s="26"/>
-      <c r="AC99" s="26"/>
-      <c r="AD99" s="26"/>
-      <c r="AE99" s="26"/>
-      <c r="AF99" s="26"/>
-      <c r="AG99" s="26"/>
-      <c r="AH99" s="129"/>
-    </row>
-    <row r="100" spans="2:34" x14ac:dyDescent="0.35">
-      <c r="B100" s="25"/>
-      <c r="C100" s="26"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="H100" s="46">
-        <v>6</v>
-      </c>
-      <c r="I100" s="46">
+      <c r="I100" s="45">
         <v>12.010999999999999</v>
       </c>
-      <c r="J100" s="47">
+      <c r="J100" s="46">
         <f>((SQRT(1-(1/I100)^2*SIN(RADIANS(165))^2)+1/I100*COS(RADIANS(165)))/(1+1/I100))^2</f>
         <v>0.72027206504080021</v>
       </c>
-      <c r="K100" s="50">
+      <c r="K100" s="49">
         <f>$D$99*1000*J100</f>
         <v>3601.3603252040011</v>
       </c>
-      <c r="L100" s="48">
+      <c r="L100" s="47">
         <v>339</v>
       </c>
-      <c r="M100" s="26"/>
-      <c r="N100" s="26"/>
-      <c r="O100" s="26"/>
-      <c r="P100" s="26"/>
-      <c r="Q100" s="26"/>
-      <c r="R100" s="26"/>
-      <c r="S100" s="85"/>
-      <c r="T100" s="26"/>
-      <c r="U100" s="26"/>
-      <c r="V100" s="26"/>
-      <c r="W100" s="82"/>
-      <c r="X100" s="26"/>
-      <c r="Y100" s="26"/>
-      <c r="Z100" s="26"/>
-      <c r="AA100" s="26"/>
-      <c r="AB100" s="26"/>
-      <c r="AC100" s="26"/>
-      <c r="AD100" s="26"/>
-      <c r="AE100" s="26"/>
-      <c r="AF100" s="26"/>
-      <c r="AG100" s="26"/>
-      <c r="AH100" s="129"/>
-    </row>
-    <row r="101" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH100" s="124"/>
+    </row>
+    <row r="101" spans="2:34" ht="15" thickBot="1">
       <c r="B101" s="25"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="26"/>
-      <c r="E101" s="26"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" s="41">
+      <c r="G101" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" s="40">
         <v>8</v>
       </c>
-      <c r="I101" s="42">
+      <c r="I101" s="41">
         <v>15.999000000000001</v>
       </c>
-      <c r="J101" s="43">
+      <c r="J101" s="42">
         <f t="shared" ref="J101:J103" si="10">((SQRT(1-(1/I101)^2*SIN(RADIANS(165))^2)+1/I101*COS(RADIANS(165)))/(1+1/I101))^2</f>
         <v>0.78185798881983415</v>
       </c>
-      <c r="K101" s="51">
+      <c r="K101" s="50">
         <f t="shared" ref="K101:K105" si="11">$D$99*1000*J101</f>
         <v>3909.289944099171</v>
       </c>
-      <c r="L101" s="44">
+      <c r="L101" s="43">
         <v>370.5</v>
       </c>
-      <c r="M101" s="26"/>
-      <c r="N101" s="26"/>
-      <c r="O101" s="26"/>
-      <c r="P101" s="26"/>
-      <c r="Q101" s="26"/>
-      <c r="R101" s="26"/>
-      <c r="S101" s="85"/>
-      <c r="T101" s="26"/>
-      <c r="U101" s="26"/>
-      <c r="V101" s="26"/>
-      <c r="W101" s="82"/>
-      <c r="X101" s="26"/>
-      <c r="Y101" s="26"/>
-      <c r="Z101" s="26"/>
-      <c r="AA101" s="26"/>
-      <c r="AB101" s="26"/>
-      <c r="AC101" s="26"/>
-      <c r="AD101" s="26"/>
-      <c r="AE101" s="26"/>
-      <c r="AF101" s="26"/>
-      <c r="AG101" s="26"/>
-      <c r="AH101" s="129"/>
-    </row>
-    <row r="102" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH101" s="124"/>
+    </row>
+    <row r="102" spans="2:34" ht="15" thickBot="1">
       <c r="B102" s="25"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="131">
+      <c r="D102" s="126">
         <f t="array" ref="D102:E105">LINEST(K100:K105,L100:L105,TRUE,TRUE)</f>
-        <v>9.80127738708428</v>
-      </c>
-      <c r="E102" s="132">
-        <v>294.51733917568345</v>
-      </c>
-      <c r="F102" s="26"/>
+        <v>9.8332864316198414</v>
+      </c>
+      <c r="E102" s="127">
+        <v>268.62608299534759</v>
+      </c>
       <c r="G102" s="22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H102" s="21">
         <v>13</v>
@@ -12822,266 +10971,145 @@
       <c r="I102" s="21">
         <v>26.98</v>
       </c>
-      <c r="J102" s="39">
+      <c r="J102" s="38">
         <f t="shared" si="10"/>
         <v>0.86433057478706143</v>
       </c>
-      <c r="K102" s="52">
-        <f t="shared" si="11"/>
-        <v>4321.6528739353071</v>
+      <c r="K102" s="51">
+        <f>(5000-88.5)*J102</f>
+        <v>4245.159618066652</v>
       </c>
       <c r="L102" s="23">
         <v>405</v>
       </c>
-      <c r="M102" s="26"/>
-      <c r="N102" s="26"/>
-      <c r="O102" s="26"/>
-      <c r="P102" s="26"/>
-      <c r="Q102" s="26"/>
-      <c r="R102" s="26"/>
-      <c r="S102" s="85"/>
-      <c r="T102" s="26"/>
-      <c r="U102" s="26"/>
-      <c r="V102" s="26"/>
-      <c r="W102" s="82"/>
-      <c r="X102" s="26"/>
-      <c r="Y102" s="26"/>
-      <c r="Z102" s="26"/>
-      <c r="AA102" s="26"/>
-      <c r="AB102" s="26"/>
-      <c r="AC102" s="26"/>
-      <c r="AD102" s="26"/>
-      <c r="AE102" s="26"/>
-      <c r="AF102" s="26"/>
-      <c r="AG102" s="26"/>
-      <c r="AH102" s="129"/>
-    </row>
-    <row r="103" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH102" s="124"/>
+    </row>
+    <row r="103" spans="2:34">
       <c r="B103" s="25"/>
-      <c r="C103" s="26"/>
       <c r="D103" s="25">
-        <v>0.28321744167471208</v>
-      </c>
-      <c r="E103" s="129">
-        <v>117.04882382677867</v>
-      </c>
-      <c r="F103" s="26"/>
-      <c r="G103" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="28">
+        <v>7.8457189141303008E-2</v>
+      </c>
+      <c r="E103" s="124">
+        <v>32.424986453666527</v>
+      </c>
+      <c r="G103" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" s="27">
         <v>14</v>
       </c>
-      <c r="I103" s="28">
+      <c r="I103" s="27">
         <v>28.09</v>
       </c>
-      <c r="J103" s="37">
+      <c r="J103" s="36">
         <f t="shared" si="10"/>
         <v>0.86932910407021868</v>
       </c>
-      <c r="K103" s="53">
+      <c r="K103" s="52">
         <f t="shared" si="11"/>
         <v>4346.6455203510932</v>
       </c>
-      <c r="L103" s="29">
+      <c r="L103" s="28">
         <v>413.5</v>
       </c>
-      <c r="M103" s="26"/>
-      <c r="N103" s="26"/>
-      <c r="O103" s="26"/>
-      <c r="P103" s="26"/>
-      <c r="Q103" s="26"/>
-      <c r="R103" s="26"/>
-      <c r="S103" s="85"/>
-      <c r="T103" s="26"/>
-      <c r="U103" s="26"/>
-      <c r="V103" s="26"/>
-      <c r="W103" s="82"/>
-      <c r="X103" s="26"/>
-      <c r="Y103" s="26"/>
-      <c r="Z103" s="26"/>
-      <c r="AA103" s="26"/>
-      <c r="AB103" s="26"/>
-      <c r="AC103" s="26"/>
-      <c r="AD103" s="26"/>
-      <c r="AE103" s="26"/>
-      <c r="AF103" s="26"/>
-      <c r="AG103" s="26"/>
-      <c r="AH103" s="129"/>
-    </row>
-    <row r="104" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH103" s="124"/>
+    </row>
+    <row r="104" spans="2:34">
       <c r="B104" s="25"/>
-      <c r="C104" s="26"/>
       <c r="D104" s="25">
-        <v>0.99667120895590811</v>
-      </c>
-      <c r="E104" s="129">
-        <v>32.714628413016257</v>
-      </c>
-      <c r="F104" s="26"/>
-      <c r="G104" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H104" s="30">
+        <v>0.99974542396027632</v>
+      </c>
+      <c r="E104" s="124">
+        <v>9.0626402594068676</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H104" s="29">
         <v>50</v>
       </c>
-      <c r="I104" s="30">
+      <c r="I104" s="29">
         <v>116</v>
       </c>
-      <c r="J104" s="31">
+      <c r="J104" s="30">
         <f>((SQRT(1-(1/I104)^2*SIN(RADIANS(165))^2)+1/I104*COS(RADIANS(165)))/(1+1/I104))^2</f>
         <v>0.96667191113339779</v>
       </c>
-      <c r="K104" s="54">
+      <c r="K104" s="53">
         <f t="shared" si="11"/>
         <v>4833.3595556669889</v>
       </c>
-      <c r="L104" s="35">
+      <c r="L104" s="34">
         <v>463.5</v>
       </c>
-      <c r="M104" s="26"/>
-      <c r="N104" s="26"/>
-      <c r="O104" s="26"/>
-      <c r="P104" s="26"/>
-      <c r="Q104" s="26"/>
-      <c r="R104" s="26"/>
-      <c r="S104" s="85"/>
-      <c r="T104" s="26"/>
-      <c r="U104" s="26"/>
-      <c r="V104" s="26"/>
-      <c r="W104" s="82"/>
-      <c r="X104" s="26"/>
-      <c r="Y104" s="26"/>
-      <c r="Z104" s="26"/>
-      <c r="AA104" s="26"/>
-      <c r="AB104" s="26"/>
-      <c r="AC104" s="26"/>
-      <c r="AD104" s="26"/>
-      <c r="AE104" s="26"/>
-      <c r="AF104" s="26"/>
-      <c r="AG104" s="26"/>
-      <c r="AH104" s="129"/>
-    </row>
-    <row r="105" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH104" s="124"/>
+    </row>
+    <row r="105" spans="2:34" ht="15" thickBot="1">
       <c r="B105" s="25"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="61">
-        <v>1197.637455465825</v>
-      </c>
-      <c r="E105" s="130">
+      <c r="D105" s="60">
+        <v>15708.397774515663</v>
+      </c>
+      <c r="E105" s="125">
         <v>4</v>
       </c>
-      <c r="F105" s="26"/>
-      <c r="G105" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="H105" s="34">
+      <c r="G105" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="33">
         <v>78</v>
       </c>
-      <c r="I105" s="34">
+      <c r="I105" s="33">
         <v>195.1</v>
       </c>
-      <c r="J105" s="38">
+      <c r="J105" s="37">
         <f>((SQRT(1-(1/I105)^2*SIN(RADIANS(165))^2)+1/I105*COS(RADIANS(165)))/(1+1/I105))^2</f>
         <v>0.9800485317759321</v>
       </c>
-      <c r="K105" s="55">
+      <c r="K105" s="54">
         <f t="shared" si="11"/>
         <v>4900.2426588796607</v>
       </c>
-      <c r="L105" s="36">
+      <c r="L105" s="35">
         <v>472</v>
       </c>
-      <c r="M105" s="26"/>
-      <c r="N105" s="26"/>
-      <c r="O105" s="26"/>
-      <c r="P105" s="26"/>
-      <c r="Q105" s="26"/>
-      <c r="R105" s="26"/>
-      <c r="S105" s="85"/>
-      <c r="T105" s="26"/>
-      <c r="U105" s="26"/>
-      <c r="V105" s="26"/>
-      <c r="W105" s="82"/>
-      <c r="X105" s="26"/>
-      <c r="Y105" s="26"/>
-      <c r="Z105" s="26"/>
-      <c r="AA105" s="26"/>
-      <c r="AB105" s="26"/>
-      <c r="AC105" s="26"/>
-      <c r="AD105" s="26"/>
-      <c r="AE105" s="26"/>
-      <c r="AF105" s="26"/>
-      <c r="AG105" s="26"/>
-      <c r="AH105" s="129"/>
-    </row>
-    <row r="106" spans="2:34" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH105" s="124"/>
+    </row>
+    <row r="106" spans="2:34" ht="44.1" thickBot="1">
       <c r="B106" s="25"/>
-      <c r="C106" s="26"/>
-      <c r="D106" s="26"/>
-      <c r="E106" s="26"/>
-      <c r="F106" s="26"/>
-      <c r="G106" s="26"/>
-      <c r="H106" s="26"/>
-      <c r="I106" s="26"/>
-      <c r="J106" s="26"/>
-      <c r="K106" s="26"/>
-      <c r="L106" s="26"/>
       <c r="M106" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R106" s="26"/>
-      <c r="S106" s="85"/>
-      <c r="T106" s="26"/>
-      <c r="U106" s="26"/>
-      <c r="V106" s="26"/>
-      <c r="W106" s="82"/>
-      <c r="X106" s="26"/>
+        <v>23</v>
+      </c>
       <c r="Y106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z106" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA106" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AB106" s="7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AC106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD106" s="26"/>
-      <c r="AE106" s="26"/>
-      <c r="AF106" s="26"/>
-      <c r="AG106" s="26"/>
-      <c r="AH106" s="129"/>
-    </row>
-    <row r="107" spans="2:34" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="AH106" s="124"/>
+    </row>
+    <row r="107" spans="2:34">
       <c r="B107" s="25"/>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="26"/>
-      <c r="H107" s="26"/>
-      <c r="I107" s="26"/>
-      <c r="J107" s="26"/>
-      <c r="K107" s="26"/>
-      <c r="L107" s="26"/>
       <c r="M107" s="4">
         <v>34.93</v>
       </c>
@@ -13100,418 +11128,255 @@
         <f>(($J$47/COS(RADIANS(0))*$N$107)+(1/COS(RADIANS(180-165))*$P$107))</f>
         <v>51.700128141963091</v>
       </c>
-      <c r="R107" s="26"/>
-      <c r="S107" s="85"/>
-      <c r="T107" s="26"/>
-      <c r="U107" s="26"/>
-      <c r="V107" s="26"/>
-      <c r="W107" s="82"/>
-      <c r="X107" s="26"/>
       <c r="Y107" s="17">
-        <v>58.39</v>
+        <v>57.71</v>
       </c>
       <c r="Z107" s="11">
         <f>Y107*$E$1/10</f>
-        <v>15.759460999999998</v>
+        <v>15.575928999999999</v>
       </c>
       <c r="AA107" s="17">
-        <v>63.39</v>
+        <v>64.22</v>
       </c>
       <c r="AB107" s="4">
         <f>AA107*$E$1/10</f>
-        <v>17.108961000000001</v>
+        <v>17.332978000000001</v>
       </c>
       <c r="AC107" s="10">
         <f>(($J$102/COS(RADIANS(0))*Z107)+(1/COS(RADIANS(180-165))*AB107))</f>
-        <v>31.333883779329351</v>
-      </c>
-      <c r="AD107" s="26"/>
-      <c r="AE107" s="26"/>
-      <c r="AF107" s="26"/>
-      <c r="AG107" s="26"/>
-      <c r="AH107" s="129"/>
-    </row>
-    <row r="108" spans="2:34" x14ac:dyDescent="0.35">
+        <v>31.407170924384459</v>
+      </c>
+      <c r="AH107" s="124"/>
+    </row>
+    <row r="108" spans="2:34">
       <c r="B108" s="25"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="26"/>
-      <c r="E108" s="26"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="26"/>
-      <c r="H108" s="26"/>
-      <c r="I108" s="26"/>
-      <c r="J108" s="26"/>
-      <c r="K108" s="26"/>
-      <c r="L108" s="26"/>
-      <c r="M108" s="26"/>
-      <c r="N108" s="26"/>
-      <c r="O108" s="26"/>
-      <c r="P108" s="26"/>
-      <c r="Q108" s="26"/>
-      <c r="R108" s="26"/>
-      <c r="S108" s="85"/>
-      <c r="T108" s="26"/>
-      <c r="U108" s="26"/>
-      <c r="V108" s="26"/>
-      <c r="W108" s="82"/>
-      <c r="X108" s="26"/>
-      <c r="Y108" s="26"/>
-      <c r="Z108" s="26"/>
-      <c r="AA108" s="26"/>
-      <c r="AB108" s="26"/>
-      <c r="AC108" s="26"/>
-      <c r="AD108" s="26"/>
-      <c r="AE108" s="26"/>
-      <c r="AF108" s="26"/>
-      <c r="AG108" s="26"/>
-      <c r="AH108" s="129"/>
-    </row>
-    <row r="109" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH108" s="124"/>
+    </row>
+    <row r="109" spans="2:34" ht="15" thickBot="1">
       <c r="B109" s="25"/>
-      <c r="C109" s="26"/>
-      <c r="D109" s="26"/>
-      <c r="E109" s="26"/>
-      <c r="F109" s="26"/>
-      <c r="G109" s="26"/>
-      <c r="H109" s="26"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="26"/>
-      <c r="K109" s="26"/>
-      <c r="L109" s="26"/>
-      <c r="M109" s="26"/>
-      <c r="N109" s="26"/>
-      <c r="O109" s="26"/>
-      <c r="P109" s="26"/>
-      <c r="Q109" s="26"/>
-      <c r="R109" s="26"/>
-      <c r="S109" s="85"/>
-      <c r="T109" s="26"/>
-      <c r="U109" s="26"/>
-      <c r="V109" s="26"/>
-      <c r="W109" s="82"/>
-      <c r="X109" s="26"/>
-      <c r="Y109" s="26"/>
-      <c r="Z109" s="26"/>
-      <c r="AA109" s="26"/>
-      <c r="AB109" s="26"/>
-      <c r="AC109" s="26"/>
-      <c r="AD109" s="26"/>
-      <c r="AE109" s="26"/>
-      <c r="AF109" s="26"/>
-      <c r="AG109" s="26"/>
-      <c r="AH109" s="129"/>
-    </row>
-    <row r="110" spans="2:34" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AH109" s="124"/>
+    </row>
+    <row r="110" spans="2:34" ht="29.45" thickBot="1">
       <c r="B110" s="25"/>
-      <c r="C110" s="26"/>
-      <c r="D110" s="26"/>
-      <c r="E110" s="26"/>
-      <c r="F110" s="26"/>
-      <c r="G110" s="26"/>
-      <c r="H110" s="26"/>
-      <c r="I110" s="26"/>
-      <c r="J110" s="26"/>
-      <c r="K110" s="26"/>
-      <c r="L110" s="26"/>
       <c r="M110" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N110" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O110" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P110" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q110" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="R110" s="69"/>
+      <c r="S110" s="82"/>
+      <c r="T110" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="U110" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="V110" s="93"/>
+      <c r="W110" s="94"/>
+      <c r="Z110" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA110" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB110" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC110" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD110" s="72"/>
+      <c r="AE110" s="72"/>
+      <c r="AF110" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH110" s="124"/>
+    </row>
+    <row r="111" spans="2:34" ht="15" thickBot="1">
+      <c r="B111" s="25"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="64">
+        <v>463.5</v>
+      </c>
+      <c r="O111" s="65">
+        <v>454.5</v>
+      </c>
+      <c r="P111" s="98">
+        <f>(N111-O111)*D102</f>
+        <v>88.499577884578571</v>
+      </c>
+      <c r="Q111" s="104">
+        <f>P111*10^3/Q107</f>
+        <v>1711.7864319710789</v>
+      </c>
+      <c r="R111" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="N110" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="O110" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="P110" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q110" s="104" t="s">
-        <v>41</v>
-      </c>
-      <c r="R110" s="70"/>
-      <c r="S110" s="86"/>
-      <c r="T110" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="U110" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="V110" s="98"/>
-      <c r="W110" s="99"/>
-      <c r="X110" s="26"/>
-      <c r="Y110" s="26"/>
-      <c r="Z110" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA110" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB110" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC110" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD110" s="73"/>
-      <c r="AE110" s="73"/>
-      <c r="AF110" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG110" s="26"/>
-      <c r="AH110" s="129"/>
-    </row>
-    <row r="111" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B111" s="25"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26"/>
-      <c r="G111" s="26"/>
-      <c r="H111" s="26"/>
-      <c r="I111" s="26"/>
-      <c r="J111" s="26"/>
-      <c r="K111" s="26"/>
-      <c r="L111" s="26"/>
-      <c r="M111" s="18"/>
-      <c r="N111" s="65">
-        <v>463.5</v>
-      </c>
-      <c r="O111" s="66">
-        <v>454.5</v>
-      </c>
-      <c r="P111" s="103">
-        <f>(N111-O111)*D102</f>
-        <v>88.211496483758523</v>
-      </c>
-      <c r="Q111" s="109">
-        <f>P111*10^3/Q107</f>
-        <v>1706.2142716849573</v>
-      </c>
-      <c r="R111" s="110" t="s">
-        <v>40</v>
-      </c>
-      <c r="S111" s="111">
+      <c r="S111" s="106">
         <f>Q111/D102*D103</f>
-        <v>49.302720644584134</v>
-      </c>
-      <c r="T111" s="112">
+        <v>13.657890756727152</v>
+      </c>
+      <c r="T111" s="107">
         <v>1543</v>
       </c>
-      <c r="U111" s="113">
+      <c r="U111" s="108">
         <v>1708</v>
       </c>
-      <c r="V111" s="114" t="s">
-        <v>40</v>
-      </c>
-      <c r="W111" s="115">
+      <c r="V111" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W111" s="110">
         <v>59</v>
       </c>
-      <c r="X111" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y111" s="26"/>
-      <c r="Z111" s="116">
+      <c r="X111" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z111" s="111">
         <v>404</v>
       </c>
       <c r="AA111" s="16">
         <v>401</v>
       </c>
-      <c r="AB111" s="71">
+      <c r="AB111" s="70">
         <f>(Z111-AA111)*D102</f>
-        <v>29.40383216125284</v>
-      </c>
-      <c r="AC111" s="117">
+        <v>29.499859294859526</v>
+      </c>
+      <c r="AC111" s="112">
         <f>AB111*10^3/AC107</f>
-        <v>938.40369002230921</v>
-      </c>
-      <c r="AD111" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE111" s="122">
+        <v>939.27146019878853</v>
+      </c>
+      <c r="AD111" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE111" s="117">
         <f>AC111/D102*D103</f>
-        <v>27.116087204760856</v>
-      </c>
-      <c r="AF111" s="123">
+        <v>7.4941983151104852</v>
+      </c>
+      <c r="AF111" s="118">
         <v>59.1</v>
       </c>
-      <c r="AG111" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH111" s="129"/>
-    </row>
-    <row r="112" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG111" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH111" s="124"/>
+    </row>
+    <row r="112" spans="2:34" ht="15" thickBot="1">
       <c r="B112" s="25"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="26"/>
-      <c r="E112" s="26"/>
-      <c r="F112" s="26"/>
-      <c r="G112" s="26"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="26"/>
-      <c r="K112" s="26"/>
-      <c r="L112" s="26"/>
-      <c r="M112" s="26"/>
-      <c r="N112" s="26"/>
-      <c r="O112" s="26"/>
-      <c r="P112" s="26"/>
-      <c r="Q112" s="107"/>
-      <c r="R112" s="74"/>
-      <c r="S112" s="108"/>
-      <c r="T112" s="100"/>
-      <c r="U112" s="100"/>
-      <c r="V112" s="74"/>
-      <c r="W112" s="105"/>
-      <c r="X112" s="26"/>
-      <c r="Y112" s="26"/>
-      <c r="Z112" s="26"/>
-      <c r="AA112" s="26"/>
-      <c r="AB112" s="26"/>
-      <c r="AC112" s="69"/>
-      <c r="AD112" s="68"/>
-      <c r="AE112" s="87"/>
-      <c r="AF112" s="78"/>
-      <c r="AG112" s="26"/>
-      <c r="AH112" s="129"/>
-    </row>
-    <row r="113" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q112" s="102"/>
+      <c r="R112" s="73"/>
+      <c r="S112" s="103"/>
+      <c r="T112" s="95"/>
+      <c r="U112" s="95"/>
+      <c r="V112" s="73"/>
+      <c r="W112" s="100"/>
+      <c r="AC112" s="68"/>
+      <c r="AD112" s="67"/>
+      <c r="AE112" s="83"/>
+      <c r="AF112" s="76"/>
+      <c r="AH112" s="124"/>
+    </row>
+    <row r="113" spans="2:34" ht="15" thickBot="1">
       <c r="B113" s="25"/>
-      <c r="C113" s="26"/>
-      <c r="D113" s="26"/>
-      <c r="E113" s="26"/>
-      <c r="F113" s="26"/>
-      <c r="G113" s="26"/>
-      <c r="H113" s="26"/>
-      <c r="I113" s="26"/>
-      <c r="J113" s="26"/>
-      <c r="K113" s="26"/>
-      <c r="L113" s="26"/>
-      <c r="M113" s="26"/>
-      <c r="N113" s="26"/>
-      <c r="O113" s="26"/>
-      <c r="P113" s="26"/>
-      <c r="Q113" s="94">
+      <c r="Q113" s="89">
         <f>Q111*$B$1*10^(-7)*10^3</f>
-        <v>1.2472426326017036</v>
-      </c>
-      <c r="R113" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="S113" s="93">
+        <v>1.2513158817708583</v>
+      </c>
+      <c r="R113" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S113" s="88">
         <f>S111*$B$1*10^(-7)*10^3</f>
-        <v>3.6040288791190998E-2</v>
-      </c>
-      <c r="T113" s="79">
+        <v>9.9839181431675469E-3</v>
+      </c>
+      <c r="T113" s="131">
         <f>T111*$B$1*10^(-7)*10^3</f>
         <v>1.1279330000000001</v>
       </c>
-      <c r="U113" s="95">
+      <c r="U113" s="90">
         <f>U111*$B$1*10^(-7)*10^3</f>
         <v>1.248548</v>
       </c>
-      <c r="V113" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="W113" s="106">
+      <c r="V113" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="W113" s="101">
         <f>W111*$B$1*10^(-7)*10^3</f>
         <v>4.3128999999999994E-2</v>
       </c>
-      <c r="X113" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y113" s="26"/>
-      <c r="Z113" s="26"/>
-      <c r="AA113" s="26"/>
-      <c r="AB113" s="26"/>
-      <c r="AC113" s="118">
+      <c r="X113" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC113" s="113">
         <f>AC111*$E$1/10</f>
-        <v>253.27515593702122</v>
-      </c>
-      <c r="AD113" s="119" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE113" s="120">
+        <v>253.50936710765299</v>
+      </c>
+      <c r="AD113" s="114" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE113" s="115">
         <f>AE111*$E$1*10^(-7)*10^6</f>
-        <v>7.3186319365649535</v>
-      </c>
-      <c r="AF113" s="124">
+        <v>2.0226841252483196</v>
+      </c>
+      <c r="AF113" s="119">
         <f>AF111*$E$1/10</f>
         <v>15.951089999999999</v>
       </c>
-      <c r="AG113" s="67" t="s">
+      <c r="AG113" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="AH113" s="129"/>
-    </row>
-    <row r="114" spans="2:34" x14ac:dyDescent="0.35">
+      <c r="AH113" s="124"/>
+    </row>
+    <row r="114" spans="2:34">
       <c r="B114" s="25"/>
-      <c r="C114" s="26"/>
-      <c r="D114" s="26"/>
-      <c r="E114" s="26"/>
-      <c r="F114" s="26"/>
-      <c r="G114" s="26"/>
-      <c r="H114" s="26"/>
-      <c r="I114" s="26"/>
-      <c r="J114" s="26"/>
-      <c r="K114" s="26"/>
-      <c r="L114" s="26"/>
-      <c r="M114" s="26"/>
-      <c r="N114" s="26"/>
-      <c r="O114" s="26"/>
-      <c r="P114" s="26"/>
-      <c r="Q114" s="26"/>
-      <c r="R114" s="26"/>
-      <c r="S114" s="85"/>
-      <c r="T114" s="26"/>
-      <c r="U114" s="74"/>
-      <c r="V114" s="74"/>
-      <c r="W114" s="89"/>
-      <c r="X114" s="26"/>
-      <c r="Y114" s="26"/>
-      <c r="Z114" s="26"/>
-      <c r="AA114" s="26"/>
-      <c r="AB114" s="26"/>
-      <c r="AC114" s="26"/>
-      <c r="AD114" s="26"/>
-      <c r="AE114" s="26"/>
-      <c r="AF114" s="26"/>
-      <c r="AG114" s="26"/>
-      <c r="AH114" s="129"/>
-    </row>
-    <row r="115" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B115" s="61"/>
-      <c r="C115" s="62"/>
-      <c r="D115" s="62"/>
-      <c r="E115" s="62"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="62"/>
-      <c r="H115" s="62"/>
-      <c r="I115" s="62"/>
-      <c r="J115" s="62"/>
-      <c r="K115" s="62"/>
-      <c r="L115" s="62"/>
-      <c r="M115" s="62"/>
-      <c r="N115" s="62"/>
-      <c r="O115" s="62"/>
-      <c r="P115" s="62"/>
-      <c r="Q115" s="62"/>
-      <c r="R115" s="62"/>
-      <c r="S115" s="88"/>
-      <c r="T115" s="62"/>
-      <c r="U115" s="75"/>
-      <c r="V115" s="75"/>
-      <c r="W115" s="90"/>
-      <c r="X115" s="62"/>
-      <c r="Y115" s="62"/>
-      <c r="Z115" s="62"/>
-      <c r="AA115" s="62"/>
-      <c r="AB115" s="62"/>
-      <c r="AC115" s="62"/>
-      <c r="AD115" s="62"/>
-      <c r="AE115" s="62"/>
-      <c r="AF115" s="62"/>
-      <c r="AG115" s="62"/>
-      <c r="AH115" s="130"/>
+      <c r="U114" s="73"/>
+      <c r="V114" s="73"/>
+      <c r="W114" s="85"/>
+      <c r="AH114" s="124"/>
+    </row>
+    <row r="115" spans="2:34" ht="15" thickBot="1">
+      <c r="B115" s="60"/>
+      <c r="C115" s="61"/>
+      <c r="D115" s="61"/>
+      <c r="E115" s="61"/>
+      <c r="F115" s="61"/>
+      <c r="G115" s="61"/>
+      <c r="H115" s="61"/>
+      <c r="I115" s="61"/>
+      <c r="J115" s="61"/>
+      <c r="K115" s="61"/>
+      <c r="L115" s="61"/>
+      <c r="M115" s="61"/>
+      <c r="N115" s="61"/>
+      <c r="O115" s="61"/>
+      <c r="P115" s="61"/>
+      <c r="Q115" s="61"/>
+      <c r="R115" s="61"/>
+      <c r="S115" s="84"/>
+      <c r="T115" s="61"/>
+      <c r="U115" s="74"/>
+      <c r="V115" s="74"/>
+      <c r="W115" s="86"/>
+      <c r="X115" s="61"/>
+      <c r="Y115" s="61"/>
+      <c r="Z115" s="61"/>
+      <c r="AA115" s="61"/>
+      <c r="AB115" s="61"/>
+      <c r="AC115" s="61"/>
+      <c r="AD115" s="61"/>
+      <c r="AE115" s="61"/>
+      <c r="AF115" s="61"/>
+      <c r="AG115" s="61"/>
+      <c r="AH115" s="125"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
